--- a/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/stock_score_patterns/S01_Missing_Adjusted_EW.xlsx
+++ b/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/outputs/stock_score_patterns/S01_Missing_Adjusted_EW.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Scenario_Config" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Factor_Map!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Factor_Map!$A$1:$K$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">FactorScore_001!$A$1:$D$577</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Scenario_Config!$A$1:$B$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">StockScore_001!$A$1:$H$73</definedName>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="199">
   <si>
     <t>個別銘柄スコア比較: S01_Missing_Adjusted_EW</t>
   </si>
@@ -103,6 +103,9 @@
     <t>Factor_Code</t>
   </si>
   <si>
+    <t>Base_Factor_Code</t>
+  </si>
+  <si>
     <t>Factor_Name_JP</t>
   </si>
   <si>
@@ -112,6 +115,18 @@
     <t>Factor_Group</t>
   </si>
   <si>
+    <t>Feature_Type</t>
+  </si>
+  <si>
+    <t>Rule_ID</t>
+  </si>
+  <si>
+    <t>Source_Lag_Periods</t>
+  </si>
+  <si>
+    <t>Effective_Target_Gap_Periods</t>
+  </si>
+  <si>
     <t>Direction</t>
   </si>
   <si>
@@ -121,15 +136,39 @@
     <t>FA0101</t>
   </si>
   <si>
+    <t>FA0101__DIFF_P1_L1</t>
+  </si>
+  <si>
+    <t>FA0101__MADEV_W12_L1</t>
+  </si>
+  <si>
+    <t>FA0101__EXPDEV_L1</t>
+  </si>
+  <si>
     <t>FA0102</t>
   </si>
   <si>
+    <t>FA0102__DIFF_P1_L1</t>
+  </si>
+  <si>
+    <t>FA0102__MADEV_W12_L1</t>
+  </si>
+  <si>
+    <t>FA0102__EXPDEV_L1</t>
+  </si>
+  <si>
     <t>FA1001</t>
   </si>
   <si>
+    <t>FA1001__DIFF_P1_L1</t>
+  </si>
+  <si>
     <t>FA1002</t>
   </si>
   <si>
+    <t>FA1002__DIFF_P1_L1</t>
+  </si>
+  <si>
     <t>FA2001</t>
   </si>
   <si>
@@ -145,15 +184,39 @@
     <t>益回り</t>
   </si>
   <si>
+    <t>益回り 差分(1期, 情報ラグ1)</t>
+  </si>
+  <si>
+    <t>益回り 移動平均乖離(12期, 情報ラグ1)</t>
+  </si>
+  <si>
+    <t>益回り 過去平均乖離(情報ラグ1)</t>
+  </si>
+  <si>
     <t>簿価時価比率</t>
   </si>
   <si>
+    <t>簿価時価比率 差分(1期, 情報ラグ1)</t>
+  </si>
+  <si>
+    <t>簿価時価比率 移動平均乖離(12期, 情報ラグ1)</t>
+  </si>
+  <si>
+    <t>簿価時価比率 過去平均乖離(情報ラグ1)</t>
+  </si>
+  <si>
     <t>12か月モメンタム</t>
   </si>
   <si>
+    <t>12か月モメンタム 差分(1期, 情報ラグ1)</t>
+  </si>
+  <si>
     <t>6か月モメンタム</t>
   </si>
   <si>
+    <t>6か月モメンタム 差分(1期, 情報ラグ1)</t>
+  </si>
+  <si>
     <t>ROE</t>
   </si>
   <si>
@@ -169,15 +232,39 @@
     <t>Earnings Yield</t>
   </si>
   <si>
+    <t>Earnings Yield Difference(1, lag 1)</t>
+  </si>
+  <si>
+    <t>Earnings Yield Rolling Mean Deviation(12, lag 1)</t>
+  </si>
+  <si>
+    <t>Earnings Yield Expanding Mean Deviation(lag 1)</t>
+  </si>
+  <si>
     <t>Book to Price</t>
   </si>
   <si>
+    <t>Book to Price Difference(1, lag 1)</t>
+  </si>
+  <si>
+    <t>Book to Price Rolling Mean Deviation(12, lag 1)</t>
+  </si>
+  <si>
+    <t>Book to Price Expanding Mean Deviation(lag 1)</t>
+  </si>
+  <si>
     <t>12M Momentum</t>
   </si>
   <si>
+    <t>12M Momentum Difference(1, lag 1)</t>
+  </si>
+  <si>
     <t>6M Momentum</t>
   </si>
   <si>
+    <t>6M Momentum Difference(1, lag 1)</t>
+  </si>
+  <si>
     <t>Return on Equity</t>
   </si>
   <si>
@@ -200,6 +287,33 @@
   </si>
   <si>
     <t>Growth</t>
+  </si>
+  <si>
+    <t>raw</t>
+  </si>
+  <si>
+    <t>difference</t>
+  </si>
+  <si>
+    <t>rolling_mean_deviation</t>
+  </si>
+  <si>
+    <t>expanding_mean_deviation</t>
+  </si>
+  <si>
+    <t>RAW</t>
+  </si>
+  <si>
+    <t>VAL_DIFF_1</t>
+  </si>
+  <si>
+    <t>VAL_MADEV_12</t>
+  </si>
+  <si>
+    <t>VAL_EXPDEV</t>
+  </si>
+  <si>
+    <t>MOM_DIFF_1</t>
   </si>
   <si>
     <t>Date</t>
@@ -1037,18 +1151,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="28.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="24" customHeight="1">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -1067,169 +1186,584 @@
       <c r="F1" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
         <v>38</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F8" t="s">
+        <v>89</v>
+      </c>
+      <c r="G8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>58</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" t="s">
+        <v>90</v>
+      </c>
+      <c r="G9" t="s">
+        <v>94</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>2</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" t="s">
+        <v>76</v>
+      </c>
+      <c r="E11" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
         <v>46</v>
       </c>
-      <c r="D2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E2">
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" t="s">
+        <v>88</v>
+      </c>
+      <c r="G13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="I13">
+        <v>2</v>
+      </c>
+      <c r="J13">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="K13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
         <v>47</v>
       </c>
-      <c r="D3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3">
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G14" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="J14">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="K14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
         <v>48</v>
       </c>
-      <c r="D4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4">
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
+        <v>87</v>
+      </c>
+      <c r="G15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
         <v>1</v>
       </c>
-      <c r="F4">
+      <c r="J15">
+        <v>-1</v>
+      </c>
+      <c r="K15">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
         <v>49</v>
       </c>
-      <c r="D5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E5">
+      <c r="B16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>81</v>
+      </c>
+      <c r="E16" t="s">
+        <v>86</v>
+      </c>
+      <c r="F16" t="s">
+        <v>87</v>
+      </c>
+      <c r="G16" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
         <v>1</v>
       </c>
-      <c r="F5">
+      <c r="J16">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F17" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" t="s">
+        <v>91</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="J17">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7">
-        <v>-1</v>
-      </c>
-      <c r="F7">
+      <c r="K17">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F9"/>
+  <autoFilter ref="A1:K17"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1250,16 +1784,16 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>60</v>
+        <v>98</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>61</v>
+        <v>99</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>12</v>
@@ -1271,7 +1805,7 @@
         <v>16</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1279,10 +1813,10 @@
         <v>43830</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D2" s="5">
         <v>85560415380.2767</v>
@@ -1302,10 +1836,10 @@
         <v>43830</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D3" s="5">
         <v>44847863016.92906</v>
@@ -1325,10 +1859,10 @@
         <v>43830</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D4" s="5">
         <v>57166728708.00803</v>
@@ -1348,10 +1882,10 @@
         <v>43830</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D5" s="5">
         <v>84986853816.11115</v>
@@ -1371,10 +1905,10 @@
         <v>43830</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D6" s="5">
         <v>8775737376.54022</v>
@@ -1394,10 +1928,10 @@
         <v>43830</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D7" s="5">
         <v>34165740151.73718</v>
@@ -1417,10 +1951,10 @@
         <v>43830</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D8" s="5">
         <v>24467802207.68756</v>
@@ -1440,10 +1974,10 @@
         <v>43830</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D9" s="5">
         <v>25021809937.39011</v>
@@ -1463,10 +1997,10 @@
         <v>43830</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D10" s="5">
         <v>31533993807.2992</v>
@@ -1486,10 +2020,10 @@
         <v>43830</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D11" s="5">
         <v>221865697882.4229</v>
@@ -1509,10 +2043,10 @@
         <v>43830</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D12" s="5">
         <v>18470523177.13689</v>
@@ -1532,10 +2066,10 @@
         <v>43830</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D13" s="5">
         <v>116718434694.1501</v>
@@ -1555,10 +2089,10 @@
         <v>43830</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D14" s="5">
         <v>7776688126.026583</v>
@@ -1578,10 +2112,10 @@
         <v>43830</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D15" s="5">
         <v>28572132418.73036</v>
@@ -1601,10 +2135,10 @@
         <v>43830</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D16" s="5">
         <v>59001526303.47971</v>
@@ -1624,10 +2158,10 @@
         <v>43830</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D17" s="5">
         <v>73493637932.66028</v>
@@ -1647,10 +2181,10 @@
         <v>43830</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D18" s="5">
         <v>80558423749.93883</v>
@@ -1670,10 +2204,10 @@
         <v>43830</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D19" s="5">
         <v>109488510227.5492</v>
@@ -1693,10 +2227,10 @@
         <v>43830</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D20" s="5">
         <v>26176522878.61734</v>
@@ -1716,10 +2250,10 @@
         <v>43830</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D21" s="5">
         <v>32345323350.61173</v>
@@ -1739,10 +2273,10 @@
         <v>43830</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D22" s="5">
         <v>108746500411.9092</v>
@@ -1762,10 +2296,10 @@
         <v>43830</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D23" s="5">
         <v>30389078149.0353</v>
@@ -1785,10 +2319,10 @@
         <v>43830</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D24" s="5">
         <v>11260716822.03961</v>
@@ -1808,10 +2342,10 @@
         <v>43830</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="D25" s="5">
         <v>14407703215.09179</v>
@@ -1831,10 +2365,10 @@
         <v>43830</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D26" s="5">
         <v>58843898935.78035</v>
@@ -1854,10 +2388,10 @@
         <v>43830</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D27" s="5">
         <v>17514606275.44078</v>
@@ -1877,10 +2411,10 @@
         <v>43830</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D28" s="5">
         <v>90452372143.44653</v>
@@ -1900,10 +2434,10 @@
         <v>43830</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D29" s="5">
         <v>117814161400.3503</v>
@@ -1923,10 +2457,10 @@
         <v>43830</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D30" s="5">
         <v>5502185504.647385</v>
@@ -1946,10 +2480,10 @@
         <v>43830</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D31" s="5">
         <v>11003436235.19764</v>
@@ -1969,10 +2503,10 @@
         <v>43830</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D32" s="5">
         <v>49326747395.29635</v>
@@ -1992,10 +2526,10 @@
         <v>43830</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D33" s="5">
         <v>30781524408.59134</v>
@@ -2015,10 +2549,10 @@
         <v>43830</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D34" s="5">
         <v>48780148711.4302</v>
@@ -2038,10 +2572,10 @@
         <v>43830</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D35" s="5">
         <v>20010977369.63276</v>
@@ -2061,10 +2595,10 @@
         <v>43830</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D36" s="5">
         <v>99290335183.37819</v>
@@ -2084,10 +2618,10 @@
         <v>43830</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D37" s="5">
         <v>88493693155.02753</v>
@@ -2107,10 +2641,10 @@
         <v>43830</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D38" s="5">
         <v>48712318792.81991</v>
@@ -2130,10 +2664,10 @@
         <v>43830</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D39" s="5">
         <v>138671614004.0398</v>
@@ -2153,10 +2687,10 @@
         <v>43830</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D40" s="5">
         <v>65323101143.68824</v>
@@ -2176,10 +2710,10 @@
         <v>43830</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D41" s="5">
         <v>16178171265.18456</v>
@@ -2199,10 +2733,10 @@
         <v>43830</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D42" s="5">
         <v>61059050281.92678</v>
@@ -2222,10 +2756,10 @@
         <v>43830</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D43" s="5">
         <v>16632559137.14928</v>
@@ -2245,10 +2779,10 @@
         <v>43830</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C44" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D44" s="5">
         <v>116329286471.4963</v>
@@ -2268,10 +2802,10 @@
         <v>43830</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C45" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D45" s="5">
         <v>42777608641.97834</v>
@@ -2291,10 +2825,10 @@
         <v>43830</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D46" s="5">
         <v>34499775773.32378</v>
@@ -2314,10 +2848,10 @@
         <v>43830</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D47" s="5">
         <v>23749097815.79458</v>
@@ -2337,10 +2871,10 @@
         <v>43830</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C48" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D48" s="5">
         <v>137003394479.6624</v>
@@ -2360,10 +2894,10 @@
         <v>43830</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="D49" s="5">
         <v>43638039996.58843</v>
@@ -2383,10 +2917,10 @@
         <v>43830</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D50" s="5">
         <v>32065415147.10638</v>
@@ -2406,10 +2940,10 @@
         <v>43830</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D51" s="5">
         <v>29334556905.52844</v>
@@ -2429,10 +2963,10 @@
         <v>43830</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D52" s="5">
         <v>83998320271.8835</v>
@@ -2452,10 +2986,10 @@
         <v>43830</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D53" s="5">
         <v>58484883313.82817</v>
@@ -2475,10 +3009,10 @@
         <v>43830</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D54" s="5">
         <v>66391081749.29126</v>
@@ -2498,10 +3032,10 @@
         <v>43830</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C55" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D55" s="5">
         <v>73632791689.4039</v>
@@ -2521,10 +3055,10 @@
         <v>43830</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C56" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D56" s="5">
         <v>419932064796.7689</v>
@@ -2544,10 +3078,10 @@
         <v>43830</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D57" s="5">
         <v>28930169463.71919</v>
@@ -2567,10 +3101,10 @@
         <v>43830</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C58" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D58" s="5">
         <v>24406555629.84833</v>
@@ -2590,10 +3124,10 @@
         <v>43830</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C59" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D59" s="5">
         <v>19510919350.35415</v>
@@ -2613,10 +3147,10 @@
         <v>43830</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D60" s="5">
         <v>74039945905.84172</v>
@@ -2636,10 +3170,10 @@
         <v>43830</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C61" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D61" s="5">
         <v>135647613203.4858</v>
@@ -2659,10 +3193,10 @@
         <v>43830</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D62" s="5">
         <v>43023551312.55903</v>
@@ -2682,10 +3216,10 @@
         <v>43830</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D63" s="5">
         <v>17701678735.83947</v>
@@ -2705,10 +3239,10 @@
         <v>43830</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D64" s="5">
         <v>19904321888.55385</v>
@@ -2728,10 +3262,10 @@
         <v>43830</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C65" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D65" s="5">
         <v>89835148627.41884</v>
@@ -2751,10 +3285,10 @@
         <v>43830</v>
       </c>
       <c r="B66" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C66" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D66" s="5">
         <v>87197923512.74266</v>
@@ -2774,10 +3308,10 @@
         <v>43830</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C67" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D67" s="5">
         <v>78544378370.3792</v>
@@ -2797,10 +3331,10 @@
         <v>43830</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C68" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D68" s="5">
         <v>23158844347.64503</v>
@@ -2820,10 +3354,10 @@
         <v>43830</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C69" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D69" s="5">
         <v>60220740840.51485</v>
@@ -2843,10 +3377,10 @@
         <v>43830</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C70" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D70" s="5">
         <v>51884533477.52072</v>
@@ -2866,10 +3400,10 @@
         <v>43830</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C71" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D71" s="5">
         <v>59876444080.7584</v>
@@ -2889,10 +3423,10 @@
         <v>43830</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D72" s="5">
         <v>105161653870.8741</v>
@@ -2912,10 +3446,10 @@
         <v>43830</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C73" t="s">
-        <v>137</v>
+        <v>175</v>
       </c>
       <c r="D73" s="5">
         <v>59724616346.68974</v>
@@ -2949,16 +3483,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -2980,13 +3514,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>58</v>
+        <v>96</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>20</v>
@@ -2997,10 +3531,10 @@
         <v>43830</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D2" s="5">
         <v>0.7708333333333334</v>
@@ -3011,10 +3545,10 @@
         <v>43830</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D3" s="5">
         <v>0.5625</v>
@@ -3025,10 +3559,10 @@
         <v>43830</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D4" s="5">
         <v>0.6041666666666666</v>
@@ -3039,10 +3573,10 @@
         <v>43830</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5">
         <v>0.1319444444444444</v>
@@ -3053,10 +3587,10 @@
         <v>43830</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D6" s="5">
         <v>0.5486111111111112</v>
@@ -3067,10 +3601,10 @@
         <v>43830</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D7" s="5">
         <v>0.4513888888888889</v>
@@ -3081,10 +3615,10 @@
         <v>43830</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D8" s="5">
         <v>0.1458333333333333</v>
@@ -3095,10 +3629,10 @@
         <v>43830</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D9" s="5">
         <v>0.6319444444444444</v>
@@ -3109,10 +3643,10 @@
         <v>43830</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10" s="5">
         <v>0.2013888888888889</v>
@@ -3123,10 +3657,10 @@
         <v>43830</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D11" s="5">
         <v>0.9513888888888888</v>
@@ -3137,10 +3671,10 @@
         <v>43830</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D12" s="5">
         <v>0.4236111111111111</v>
@@ -3151,10 +3685,10 @@
         <v>43830</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D13" s="5">
         <v>0.8125</v>
@@ -3165,10 +3699,10 @@
         <v>43830</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D14" s="5">
         <v>0.9930555555555556</v>
@@ -3179,10 +3713,10 @@
         <v>43830</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D15" s="5">
         <v>0.5069444444444444</v>
@@ -3193,10 +3727,10 @@
         <v>43830</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D16" s="5">
         <v>0.7986111111111112</v>
@@ -3207,10 +3741,10 @@
         <v>43830</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D17" s="5">
         <v>0.9097222222222222</v>
@@ -3221,10 +3755,10 @@
         <v>43830</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D18" s="5">
         <v>0.1597222222222222</v>
@@ -3235,10 +3769,10 @@
         <v>43830</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D19" s="5">
         <v>0.2291666666666667</v>
@@ -3249,10 +3783,10 @@
         <v>43830</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D20" s="5">
         <v>0.3958333333333333</v>
@@ -3263,10 +3797,10 @@
         <v>43830</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D21" s="5">
         <v>0.03472222222222222</v>
@@ -3277,10 +3811,10 @@
         <v>43830</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D22" s="5">
         <v>0.9375</v>
@@ -3291,10 +3825,10 @@
         <v>43830</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D23" s="5">
         <v>0.1736111111111111</v>
@@ -3305,10 +3839,10 @@
         <v>43830</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D24" s="5">
         <v>0.2430555555555556</v>
@@ -3319,10 +3853,10 @@
         <v>43830</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D25" s="5">
         <v>0.6458333333333334</v>
@@ -3333,10 +3867,10 @@
         <v>43830</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D26" s="5">
         <v>0.2986111111111111</v>
@@ -3347,10 +3881,10 @@
         <v>43830</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D27" s="5">
         <v>0.3680555555555556</v>
@@ -3361,10 +3895,10 @@
         <v>43830</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C28" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D28" s="5">
         <v>0.6875</v>
@@ -3375,10 +3909,10 @@
         <v>43830</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D29" s="5">
         <v>0.3125</v>
@@ -3389,10 +3923,10 @@
         <v>43830</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D30" s="5">
         <v>0.7569444444444444</v>
@@ -3403,10 +3937,10 @@
         <v>43830</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C31" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D31" s="5">
         <v>0.6180555555555556</v>
@@ -3417,10 +3951,10 @@
         <v>43830</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D32" s="5">
         <v>0.5208333333333334</v>
@@ -3431,10 +3965,10 @@
         <v>43830</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C33" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D33" s="5">
         <v>0.3541666666666667</v>
@@ -3445,10 +3979,10 @@
         <v>43830</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D34" s="5">
         <v>0.2708333333333333</v>
@@ -3459,10 +3993,10 @@
         <v>43830</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D35" s="5">
         <v>0.8680555555555556</v>
@@ -3473,10 +4007,10 @@
         <v>43830</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D36" s="5">
         <v>0.3819444444444444</v>
@@ -3487,10 +4021,10 @@
         <v>43830</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D37" s="5">
         <v>0.6736111111111112</v>
@@ -3501,10 +4035,10 @@
         <v>43830</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C38" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D38" s="5">
         <v>0.3263888888888889</v>
@@ -3515,10 +4049,10 @@
         <v>43830</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C39" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D39" s="5">
         <v>0.5763888888888888</v>
@@ -3529,10 +4063,10 @@
         <v>43830</v>
       </c>
       <c r="B40" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C40" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D40" s="5">
         <v>0.1180555555555556</v>
@@ -3543,10 +4077,10 @@
         <v>43830</v>
       </c>
       <c r="B41" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D41" s="5">
         <v>0.7291666666666666</v>
@@ -3557,10 +4091,10 @@
         <v>43830</v>
       </c>
       <c r="B42" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D42" s="5">
         <v>0.7013888888888888</v>
@@ -3571,10 +4105,10 @@
         <v>43830</v>
       </c>
       <c r="B43" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D43" s="5">
         <v>0.3402777777777778</v>
@@ -3585,10 +4119,10 @@
         <v>43830</v>
       </c>
       <c r="B44" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D44" s="5">
         <v>0.2152777777777778</v>
@@ -3599,10 +4133,10 @@
         <v>43830</v>
       </c>
       <c r="B45" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D45" s="5">
         <v>0.8958333333333334</v>
@@ -3613,10 +4147,10 @@
         <v>43830</v>
       </c>
       <c r="B46" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D46" s="5">
         <v>0.09027777777777778</v>
@@ -3627,10 +4161,10 @@
         <v>43830</v>
       </c>
       <c r="B47" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D47" s="5">
         <v>0.8263888888888888</v>
@@ -3641,10 +4175,10 @@
         <v>43830</v>
       </c>
       <c r="B48" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D48" s="5">
         <v>0.1041666666666667</v>
@@ -3655,10 +4189,10 @@
         <v>43830</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D49" s="5">
         <v>0.8541666666666666</v>
@@ -3669,10 +4203,10 @@
         <v>43830</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C50" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D50" s="5">
         <v>0.4097222222222222</v>
@@ -3683,10 +4217,10 @@
         <v>43830</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C51" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D51" s="5">
         <v>0.4375</v>
@@ -3697,10 +4231,10 @@
         <v>43830</v>
       </c>
       <c r="B52" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D52" s="5">
         <v>0.7430555555555556</v>
@@ -3711,10 +4245,10 @@
         <v>43830</v>
       </c>
       <c r="B53" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D53" s="5">
         <v>0.9236111111111112</v>
@@ -3725,10 +4259,10 @@
         <v>43830</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D54" s="5">
         <v>0.4791666666666667</v>
@@ -3739,10 +4273,10 @@
         <v>43830</v>
       </c>
       <c r="B55" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D55" s="5">
         <v>0.0625</v>
@@ -3753,10 +4287,10 @@
         <v>43830</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D56" s="5">
         <v>0.2569444444444444</v>
@@ -3767,10 +4301,10 @@
         <v>43830</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D57" s="5">
         <v>0.7847222222222222</v>
@@ -3781,10 +4315,10 @@
         <v>43830</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D58" s="5">
         <v>0.4652777777777778</v>
@@ -3795,10 +4329,10 @@
         <v>43830</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D59" s="5">
         <v>0.04861111111111111</v>
@@ -3809,10 +4343,10 @@
         <v>43830</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D60" s="5">
         <v>0.0763888888888889</v>
@@ -3823,10 +4357,10 @@
         <v>43830</v>
       </c>
       <c r="B61" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C61" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D61" s="5">
         <v>0.4930555555555556</v>
@@ -3837,10 +4371,10 @@
         <v>43830</v>
       </c>
       <c r="B62" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C62" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D62" s="5">
         <v>0.7152777777777778</v>
@@ -3851,10 +4385,10 @@
         <v>43830</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C63" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D63" s="5">
         <v>0.5902777777777778</v>
@@ -3865,10 +4399,10 @@
         <v>43830</v>
       </c>
       <c r="B64" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D64" s="5">
         <v>0.2847222222222222</v>
@@ -3879,10 +4413,10 @@
         <v>43830</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D65" s="5">
         <v>0.006944444444444444</v>
@@ -3893,10 +4427,10 @@
         <v>43830</v>
       </c>
       <c r="B66" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D66" s="5">
         <v>0.6597222222222222</v>
@@ -3907,10 +4441,10 @@
         <v>43830</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D67" s="5">
         <v>0.02083333333333333</v>
@@ -3921,10 +4455,10 @@
         <v>43830</v>
       </c>
       <c r="B68" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C68" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D68" s="5">
         <v>0.1875</v>
@@ -3935,10 +4469,10 @@
         <v>43830</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C69" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D69" s="5">
         <v>0.9652777777777778</v>
@@ -3949,10 +4483,10 @@
         <v>43830</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C70" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D70" s="5">
         <v>0.9791666666666666</v>
@@ -3963,10 +4497,10 @@
         <v>43830</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C71" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D71" s="5">
         <v>0.8819444444444444</v>
@@ -3977,10 +4511,10 @@
         <v>43830</v>
       </c>
       <c r="B72" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C72" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D72" s="5">
         <v>0.8402777777777778</v>
@@ -3991,10 +4525,10 @@
         <v>43830</v>
       </c>
       <c r="B73" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C73" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D73" s="5">
         <v>0.5347222222222222</v>
@@ -4005,10 +4539,10 @@
         <v>43830</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D74" s="5">
         <v>0.8680555555555556</v>
@@ -4019,10 +4553,10 @@
         <v>43830</v>
       </c>
       <c r="B75" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C75" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D75" s="5">
         <v>0.8125</v>
@@ -4033,10 +4567,10 @@
         <v>43830</v>
       </c>
       <c r="B76" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C76" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D76" s="5">
         <v>0.5069444444444444</v>
@@ -4047,10 +4581,10 @@
         <v>43830</v>
       </c>
       <c r="B77" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C77" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D77" s="5">
         <v>0.2708333333333333</v>
@@ -4061,10 +4595,10 @@
         <v>43830</v>
       </c>
       <c r="B78" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C78" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D78" s="5">
         <v>0.5347222222222222</v>
@@ -4075,10 +4609,10 @@
         <v>43830</v>
       </c>
       <c r="B79" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C79" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D79" s="5">
         <v>0.3680555555555556</v>
@@ -4089,10 +4623,10 @@
         <v>43830</v>
       </c>
       <c r="B80" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C80" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D80" s="5">
         <v>0.02083333333333333</v>
@@ -4103,10 +4637,10 @@
         <v>43830</v>
       </c>
       <c r="B81" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C81" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D81" s="5">
         <v>0.3958333333333333</v>
@@ -4117,10 +4651,10 @@
         <v>43830</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C82" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D82" s="5">
         <v>0.4097222222222222</v>
@@ -4131,10 +4665,10 @@
         <v>43830</v>
       </c>
       <c r="B83" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C83" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D83" s="5">
         <v>0.8819444444444444</v>
@@ -4145,10 +4679,10 @@
         <v>43830</v>
       </c>
       <c r="B84" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D84" s="5">
         <v>0.4652777777777778</v>
@@ -4159,10 +4693,10 @@
         <v>43830</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C85" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D85" s="5">
         <v>0.5902777777777778</v>
@@ -4173,10 +4707,10 @@
         <v>43830</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C86" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D86" s="5">
         <v>0.9791666666666666</v>
@@ -4187,10 +4721,10 @@
         <v>43830</v>
       </c>
       <c r="B87" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C87" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D87" s="5">
         <v>0.7569444444444444</v>
@@ -4201,10 +4735,10 @@
         <v>43830</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D88" s="5">
         <v>0.9097222222222222</v>
@@ -4215,10 +4749,10 @@
         <v>43830</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D89" s="5">
         <v>0.9652777777777778</v>
@@ -4229,10 +4763,10 @@
         <v>43830</v>
       </c>
       <c r="B90" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D90" s="5">
         <v>0.1736111111111111</v>
@@ -4243,10 +4777,10 @@
         <v>43830</v>
       </c>
       <c r="B91" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C91" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D91" s="5">
         <v>0.2569444444444444</v>
@@ -4257,10 +4791,10 @@
         <v>43830</v>
       </c>
       <c r="B92" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C92" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D92" s="5">
         <v>0.3402777777777778</v>
@@ -4271,10 +4805,10 @@
         <v>43830</v>
       </c>
       <c r="B93" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C93" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D93" s="5">
         <v>0.03472222222222222</v>
@@ -4285,10 +4819,10 @@
         <v>43830</v>
       </c>
       <c r="B94" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C94" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D94" s="5">
         <v>0.9513888888888888</v>
@@ -4299,10 +4833,10 @@
         <v>43830</v>
       </c>
       <c r="B95" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C95" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D95" s="5">
         <v>0.09027777777777778</v>
@@ -4313,10 +4847,10 @@
         <v>43830</v>
       </c>
       <c r="B96" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D96" s="5">
         <v>0.3541666666666667</v>
@@ -4327,10 +4861,10 @@
         <v>43830</v>
       </c>
       <c r="B97" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C97" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D97" s="5">
         <v>0.3125</v>
@@ -4341,10 +4875,10 @@
         <v>43830</v>
       </c>
       <c r="B98" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C98" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D98" s="5">
         <v>0.2430555555555556</v>
@@ -4355,10 +4889,10 @@
         <v>43830</v>
       </c>
       <c r="B99" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C99" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D99" s="5">
         <v>0.8541666666666666</v>
@@ -4369,10 +4903,10 @@
         <v>43830</v>
       </c>
       <c r="B100" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D100" s="5">
         <v>0.6180555555555556</v>
@@ -4383,10 +4917,10 @@
         <v>43830</v>
       </c>
       <c r="B101" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C101" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D101" s="5">
         <v>0.2152777777777778</v>
@@ -4397,10 +4931,10 @@
         <v>43830</v>
       </c>
       <c r="B102" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D102" s="5">
         <v>0.8263888888888888</v>
@@ -4411,10 +4945,10 @@
         <v>43830</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C103" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D103" s="5">
         <v>0.6597222222222222</v>
@@ -4425,10 +4959,10 @@
         <v>43830</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C104" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D104" s="5">
         <v>0.2847222222222222</v>
@@ -4439,10 +4973,10 @@
         <v>43830</v>
       </c>
       <c r="B105" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C105" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D105" s="5">
         <v>0.2291666666666667</v>
@@ -4453,10 +4987,10 @@
         <v>43830</v>
       </c>
       <c r="B106" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C106" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D106" s="5">
         <v>0.1597222222222222</v>
@@ -4467,10 +5001,10 @@
         <v>43830</v>
       </c>
       <c r="B107" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C107" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D107" s="5">
         <v>0.6736111111111112</v>
@@ -4481,10 +5015,10 @@
         <v>43830</v>
       </c>
       <c r="B108" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C108" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D108" s="5">
         <v>0.7430555555555556</v>
@@ -4495,10 +5029,10 @@
         <v>43830</v>
       </c>
       <c r="B109" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D109" s="5">
         <v>0.9236111111111112</v>
@@ -4509,10 +5043,10 @@
         <v>43830</v>
       </c>
       <c r="B110" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C110" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D110" s="5">
         <v>0.4513888888888889</v>
@@ -4523,10 +5057,10 @@
         <v>43830</v>
       </c>
       <c r="B111" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C111" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D111" s="5">
         <v>0.6319444444444444</v>
@@ -4537,10 +5071,10 @@
         <v>43830</v>
       </c>
       <c r="B112" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C112" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D112" s="5">
         <v>0.4236111111111111</v>
@@ -4551,10 +5085,10 @@
         <v>43830</v>
       </c>
       <c r="B113" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C113" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D113" s="5">
         <v>0.7152777777777778</v>
@@ -4565,10 +5099,10 @@
         <v>43830</v>
       </c>
       <c r="B114" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C114" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D114" s="5">
         <v>0.7986111111111112</v>
@@ -4579,10 +5113,10 @@
         <v>43830</v>
       </c>
       <c r="B115" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C115" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D115" s="5">
         <v>0.8402777777777778</v>
@@ -4593,10 +5127,10 @@
         <v>43830</v>
       </c>
       <c r="B116" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C116" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D116" s="5">
         <v>0.3263888888888889</v>
@@ -4607,10 +5141,10 @@
         <v>43830</v>
       </c>
       <c r="B117" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C117" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D117" s="5">
         <v>0.7847222222222222</v>
@@ -4621,10 +5155,10 @@
         <v>43830</v>
       </c>
       <c r="B118" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C118" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D118" s="5">
         <v>0.0763888888888889</v>
@@ -4635,10 +5169,10 @@
         <v>43830</v>
       </c>
       <c r="B119" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C119" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D119" s="5">
         <v>0.4791666666666667</v>
@@ -4649,10 +5183,10 @@
         <v>43830</v>
       </c>
       <c r="B120" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C120" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D120" s="5">
         <v>0.04861111111111111</v>
@@ -4663,10 +5197,10 @@
         <v>43830</v>
       </c>
       <c r="B121" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C121" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D121" s="5">
         <v>0.5625</v>
@@ -4677,10 +5211,10 @@
         <v>43830</v>
       </c>
       <c r="B122" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D122" s="5">
         <v>0.2986111111111111</v>
@@ -4691,10 +5225,10 @@
         <v>43830</v>
       </c>
       <c r="B123" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C123" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D123" s="5">
         <v>0.5208333333333334</v>
@@ -4705,10 +5239,10 @@
         <v>43830</v>
       </c>
       <c r="B124" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C124" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D124" s="5">
         <v>0.7013888888888888</v>
@@ -4719,10 +5253,10 @@
         <v>43830</v>
       </c>
       <c r="B125" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C125" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D125" s="5">
         <v>0.6458333333333334</v>
@@ -4733,10 +5267,10 @@
         <v>43830</v>
       </c>
       <c r="B126" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C126" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D126" s="5">
         <v>0.3819444444444444</v>
@@ -4747,10 +5281,10 @@
         <v>43830</v>
       </c>
       <c r="B127" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C127" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D127" s="5">
         <v>0.2013888888888889</v>
@@ -4761,10 +5295,10 @@
         <v>43830</v>
       </c>
       <c r="B128" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C128" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D128" s="5">
         <v>0.1875</v>
@@ -4775,10 +5309,10 @@
         <v>43830</v>
       </c>
       <c r="B129" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C129" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D129" s="5">
         <v>0.6875</v>
@@ -4789,10 +5323,10 @@
         <v>43830</v>
       </c>
       <c r="B130" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C130" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D130" s="5">
         <v>0.6041666666666666</v>
@@ -4803,10 +5337,10 @@
         <v>43830</v>
       </c>
       <c r="B131" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C131" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D131" s="5">
         <v>0.1180555555555556</v>
@@ -4817,10 +5351,10 @@
         <v>43830</v>
       </c>
       <c r="B132" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C132" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D132" s="5">
         <v>0.1041666666666667</v>
@@ -4831,10 +5365,10 @@
         <v>43830</v>
       </c>
       <c r="B133" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C133" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D133" s="5">
         <v>0.1319444444444444</v>
@@ -4845,10 +5379,10 @@
         <v>43830</v>
       </c>
       <c r="B134" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C134" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D134" s="5">
         <v>0.4930555555555556</v>
@@ -4859,10 +5393,10 @@
         <v>43830</v>
       </c>
       <c r="B135" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C135" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D135" s="5">
         <v>0.5486111111111112</v>
@@ -4873,10 +5407,10 @@
         <v>43830</v>
       </c>
       <c r="B136" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C136" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D136" s="5">
         <v>0.4375</v>
@@ -4887,10 +5421,10 @@
         <v>43830</v>
       </c>
       <c r="B137" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C137" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D137" s="5">
         <v>0.0625</v>
@@ -4901,10 +5435,10 @@
         <v>43830</v>
       </c>
       <c r="B138" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C138" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D138" s="5">
         <v>0.7291666666666666</v>
@@ -4915,10 +5449,10 @@
         <v>43830</v>
       </c>
       <c r="B139" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C139" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D139" s="5">
         <v>0.006944444444444444</v>
@@ -4929,10 +5463,10 @@
         <v>43830</v>
       </c>
       <c r="B140" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C140" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D140" s="5">
         <v>0.1458333333333333</v>
@@ -4943,10 +5477,10 @@
         <v>43830</v>
       </c>
       <c r="B141" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C141" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D141" s="5">
         <v>0.9375</v>
@@ -4957,10 +5491,10 @@
         <v>43830</v>
       </c>
       <c r="B142" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C142" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D142" s="5">
         <v>0.9930555555555556</v>
@@ -4971,10 +5505,10 @@
         <v>43830</v>
       </c>
       <c r="B143" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C143" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D143" s="5">
         <v>0.5763888888888888</v>
@@ -4985,10 +5519,10 @@
         <v>43830</v>
       </c>
       <c r="B144" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C144" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D144" s="5">
         <v>0.8958333333333334</v>
@@ -4999,10 +5533,10 @@
         <v>43830</v>
       </c>
       <c r="B145" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C145" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D145" s="5">
         <v>0.7708333333333334</v>
@@ -5013,10 +5547,10 @@
         <v>43830</v>
       </c>
       <c r="B146" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C146" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D146" s="5">
         <v>0.4652777777777778</v>
@@ -5027,10 +5561,10 @@
         <v>43830</v>
       </c>
       <c r="B147" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C147" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D147" s="5">
         <v>0.7152777777777778</v>
@@ -5041,10 +5575,10 @@
         <v>43830</v>
       </c>
       <c r="B148" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C148" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D148" s="5">
         <v>0.2986111111111111</v>
@@ -5055,10 +5589,10 @@
         <v>43830</v>
       </c>
       <c r="B149" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C149" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D149" s="5">
         <v>0.9513888888888888</v>
@@ -5069,10 +5603,10 @@
         <v>43830</v>
       </c>
       <c r="B150" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C150" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D150" s="5">
         <v>0.1319444444444444</v>
@@ -5083,10 +5617,10 @@
         <v>43830</v>
       </c>
       <c r="B151" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C151" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D151" s="5">
         <v>0.3680555555555556</v>
@@ -5097,10 +5631,10 @@
         <v>43830</v>
       </c>
       <c r="B152" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C152" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D152" s="5">
         <v>0.5208333333333334</v>
@@ -5111,10 +5645,10 @@
         <v>43830</v>
       </c>
       <c r="B153" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C153" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D153" s="5">
         <v>0.8958333333333334</v>
@@ -5125,10 +5659,10 @@
         <v>43830</v>
       </c>
       <c r="B154" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C154" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D154" s="5">
         <v>0.04861111111111111</v>
@@ -5139,10 +5673,10 @@
         <v>43830</v>
       </c>
       <c r="B155" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C155" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D155" s="5">
         <v>0.6458333333333334</v>
@@ -5153,10 +5687,10 @@
         <v>43830</v>
       </c>
       <c r="B156" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C156" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D156" s="5">
         <v>0.3263888888888889</v>
@@ -5167,10 +5701,10 @@
         <v>43830</v>
       </c>
       <c r="B157" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C157" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D157" s="5">
         <v>0.1736111111111111</v>
@@ -5181,10 +5715,10 @@
         <v>43830</v>
       </c>
       <c r="B158" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C158" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D158" s="5">
         <v>0.6041666666666666</v>
@@ -5195,10 +5729,10 @@
         <v>43830</v>
       </c>
       <c r="B159" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C159" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D159" s="5">
         <v>0.7708333333333334</v>
@@ -5209,10 +5743,10 @@
         <v>43830</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C160" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D160" s="5">
         <v>0.8263888888888888</v>
@@ -5223,10 +5757,10 @@
         <v>43830</v>
       </c>
       <c r="B161" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C161" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D161" s="5">
         <v>0.0625</v>
@@ -5237,10 +5771,10 @@
         <v>43830</v>
       </c>
       <c r="B162" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C162" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D162" s="5">
         <v>0.4791666666666667</v>
@@ -5251,10 +5785,10 @@
         <v>43830</v>
       </c>
       <c r="B163" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C163" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D163" s="5">
         <v>0.3125</v>
@@ -5265,10 +5799,10 @@
         <v>43830</v>
       </c>
       <c r="B164" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C164" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D164" s="5">
         <v>0.9375</v>
@@ -5279,10 +5813,10 @@
         <v>43830</v>
       </c>
       <c r="B165" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C165" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D165" s="5">
         <v>0.09027777777777778</v>
@@ -5293,10 +5827,10 @@
         <v>43830</v>
       </c>
       <c r="B166" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C166" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D166" s="5">
         <v>0.4930555555555556</v>
@@ -5307,10 +5841,10 @@
         <v>43830</v>
       </c>
       <c r="B167" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C167" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D167" s="5">
         <v>0.4236111111111111</v>
@@ -5321,10 +5855,10 @@
         <v>43830</v>
       </c>
       <c r="B168" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C168" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D168" s="5">
         <v>0.5625</v>
@@ -5335,10 +5869,10 @@
         <v>43830</v>
       </c>
       <c r="B169" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C169" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D169" s="5">
         <v>0.1041666666666667</v>
@@ -5349,10 +5883,10 @@
         <v>43830</v>
       </c>
       <c r="B170" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C170" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D170" s="5">
         <v>0.3541666666666667</v>
@@ -5363,10 +5897,10 @@
         <v>43830</v>
       </c>
       <c r="B171" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C171" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D171" s="5">
         <v>0.9236111111111112</v>
@@ -5377,10 +5911,10 @@
         <v>43830</v>
       </c>
       <c r="B172" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C172" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D172" s="5">
         <v>0.2152777777777778</v>
@@ -5391,10 +5925,10 @@
         <v>43830</v>
       </c>
       <c r="B173" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C173" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D173" s="5">
         <v>0.7291666666666666</v>
@@ -5405,10 +5939,10 @@
         <v>43830</v>
       </c>
       <c r="B174" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C174" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D174" s="5">
         <v>0.5069444444444444</v>
@@ -5419,10 +5953,10 @@
         <v>43830</v>
       </c>
       <c r="B175" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C175" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D175" s="5">
         <v>0.02083333333333333</v>
@@ -5433,10 +5967,10 @@
         <v>43830</v>
       </c>
       <c r="B176" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C176" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D176" s="5">
         <v>0.8402777777777778</v>
@@ -5447,10 +5981,10 @@
         <v>43830</v>
       </c>
       <c r="B177" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C177" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D177" s="5">
         <v>0.3819444444444444</v>
@@ -5461,10 +5995,10 @@
         <v>43830</v>
       </c>
       <c r="B178" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C178" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D178" s="5">
         <v>0.2708333333333333</v>
@@ -5475,10 +6009,10 @@
         <v>43830</v>
       </c>
       <c r="B179" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C179" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D179" s="5">
         <v>0.7569444444444444</v>
@@ -5489,10 +6023,10 @@
         <v>43830</v>
       </c>
       <c r="B180" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C180" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D180" s="5">
         <v>0.6736111111111112</v>
@@ -5503,10 +6037,10 @@
         <v>43830</v>
       </c>
       <c r="B181" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C181" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D181" s="5">
         <v>0.8819444444444444</v>
@@ -5517,10 +6051,10 @@
         <v>43830</v>
       </c>
       <c r="B182" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C182" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D182" s="5">
         <v>0.8125</v>
@@ -5531,10 +6065,10 @@
         <v>43830</v>
       </c>
       <c r="B183" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C183" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D183" s="5">
         <v>0.7986111111111112</v>
@@ -5545,10 +6079,10 @@
         <v>43830</v>
       </c>
       <c r="B184" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C184" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D184" s="5">
         <v>0.6875</v>
@@ -5559,10 +6093,10 @@
         <v>43830</v>
       </c>
       <c r="B185" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C185" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D185" s="5">
         <v>0.1875</v>
@@ -5573,10 +6107,10 @@
         <v>43830</v>
       </c>
       <c r="B186" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C186" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D186" s="5">
         <v>0.9930555555555556</v>
@@ -5587,10 +6121,10 @@
         <v>43830</v>
       </c>
       <c r="B187" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C187" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D187" s="5">
         <v>0.0763888888888889</v>
@@ -5601,10 +6135,10 @@
         <v>43830</v>
       </c>
       <c r="B188" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C188" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D188" s="5">
         <v>0.1180555555555556</v>
@@ -5615,10 +6149,10 @@
         <v>43830</v>
       </c>
       <c r="B189" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C189" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D189" s="5">
         <v>0.4097222222222222</v>
@@ -5629,10 +6163,10 @@
         <v>43830</v>
       </c>
       <c r="B190" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C190" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D190" s="5">
         <v>0.2847222222222222</v>
@@ -5643,10 +6177,10 @@
         <v>43830</v>
       </c>
       <c r="B191" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C191" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D191" s="5">
         <v>0.6597222222222222</v>
@@ -5657,10 +6191,10 @@
         <v>43830</v>
       </c>
       <c r="B192" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C192" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D192" s="5">
         <v>0.9097222222222222</v>
@@ -5671,10 +6205,10 @@
         <v>43830</v>
       </c>
       <c r="B193" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C193" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D193" s="5">
         <v>0.8680555555555556</v>
@@ -5685,10 +6219,10 @@
         <v>43830</v>
       </c>
       <c r="B194" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C194" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D194" s="5">
         <v>0.03472222222222222</v>
@@ -5699,10 +6233,10 @@
         <v>43830</v>
       </c>
       <c r="B195" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C195" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D195" s="5">
         <v>0.006944444444444444</v>
@@ -5713,10 +6247,10 @@
         <v>43830</v>
       </c>
       <c r="B196" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C196" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D196" s="5">
         <v>0.1597222222222222</v>
@@ -5727,10 +6261,10 @@
         <v>43830</v>
       </c>
       <c r="B197" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C197" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D197" s="5">
         <v>0.4513888888888889</v>
@@ -5741,10 +6275,10 @@
         <v>43830</v>
       </c>
       <c r="B198" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C198" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D198" s="5">
         <v>0.5902777777777778</v>
@@ -5755,10 +6289,10 @@
         <v>43830</v>
       </c>
       <c r="B199" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C199" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D199" s="5">
         <v>0.9791666666666666</v>
@@ -5769,10 +6303,10 @@
         <v>43830</v>
       </c>
       <c r="B200" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C200" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D200" s="5">
         <v>0.2291666666666667</v>
@@ -5783,10 +6317,10 @@
         <v>43830</v>
       </c>
       <c r="B201" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C201" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D201" s="5">
         <v>0.5486111111111112</v>
@@ -5797,10 +6331,10 @@
         <v>43830</v>
       </c>
       <c r="B202" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C202" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D202" s="5">
         <v>0.7013888888888888</v>
@@ -5811,10 +6345,10 @@
         <v>43830</v>
       </c>
       <c r="B203" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C203" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D203" s="5">
         <v>0.2013888888888889</v>
@@ -5825,10 +6359,10 @@
         <v>43830</v>
       </c>
       <c r="B204" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C204" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D204" s="5">
         <v>0.6180555555555556</v>
@@ -5839,10 +6373,10 @@
         <v>43830</v>
       </c>
       <c r="B205" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C205" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D205" s="5">
         <v>0.4375</v>
@@ -5853,10 +6387,10 @@
         <v>43830</v>
       </c>
       <c r="B206" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C206" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D206" s="5">
         <v>0.1458333333333333</v>
@@ -5867,10 +6401,10 @@
         <v>43830</v>
       </c>
       <c r="B207" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C207" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D207" s="5">
         <v>0.7430555555555556</v>
@@ -5881,10 +6415,10 @@
         <v>43830</v>
       </c>
       <c r="B208" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C208" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D208" s="5">
         <v>0.9652777777777778</v>
@@ -5895,10 +6429,10 @@
         <v>43830</v>
       </c>
       <c r="B209" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C209" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D209" s="5">
         <v>0.5347222222222222</v>
@@ -5909,10 +6443,10 @@
         <v>43830</v>
       </c>
       <c r="B210" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C210" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D210" s="5">
         <v>0.7847222222222222</v>
@@ -5923,10 +6457,10 @@
         <v>43830</v>
       </c>
       <c r="B211" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C211" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D211" s="5">
         <v>0.3958333333333333</v>
@@ -5937,10 +6471,10 @@
         <v>43830</v>
       </c>
       <c r="B212" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C212" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D212" s="5">
         <v>0.2430555555555556</v>
@@ -5951,10 +6485,10 @@
         <v>43830</v>
       </c>
       <c r="B213" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C213" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D213" s="5">
         <v>0.5763888888888888</v>
@@ -5965,10 +6499,10 @@
         <v>43830</v>
       </c>
       <c r="B214" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C214" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D214" s="5">
         <v>0.2569444444444444</v>
@@ -5979,10 +6513,10 @@
         <v>43830</v>
       </c>
       <c r="B215" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C215" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D215" s="5">
         <v>0.3402777777777778</v>
@@ -5993,10 +6527,10 @@
         <v>43830</v>
       </c>
       <c r="B216" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C216" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D216" s="5">
         <v>0.8541666666666666</v>
@@ -6007,10 +6541,10 @@
         <v>43830</v>
       </c>
       <c r="B217" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C217" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D217" s="5">
         <v>0.6319444444444444</v>
@@ -6021,10 +6555,10 @@
         <v>43830</v>
       </c>
       <c r="B218" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C218" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D218" s="5">
         <v>0.5625</v>
@@ -6035,10 +6569,10 @@
         <v>43830</v>
       </c>
       <c r="B219" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C219" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D219" s="5">
         <v>0.8263888888888888</v>
@@ -6049,10 +6583,10 @@
         <v>43830</v>
       </c>
       <c r="B220" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C220" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D220" s="5">
         <v>0.3263888888888889</v>
@@ -6063,10 +6597,10 @@
         <v>43830</v>
       </c>
       <c r="B221" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C221" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D221" s="5">
         <v>0.9930555555555556</v>
@@ -6077,10 +6611,10 @@
         <v>43830</v>
       </c>
       <c r="B222" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C222" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D222" s="5">
         <v>0.4791666666666667</v>
@@ -6091,10 +6625,10 @@
         <v>43830</v>
       </c>
       <c r="B223" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C223" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D223" s="5">
         <v>0.3541666666666667</v>
@@ -6105,10 +6639,10 @@
         <v>43830</v>
       </c>
       <c r="B224" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C224" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D224" s="5">
         <v>0.7291666666666666</v>
@@ -6119,10 +6653,10 @@
         <v>43830</v>
       </c>
       <c r="B225" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C225" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D225" s="5">
         <v>0.9513888888888888</v>
@@ -6133,10 +6667,10 @@
         <v>43830</v>
       </c>
       <c r="B226" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C226" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D226" s="5">
         <v>0.2708333333333333</v>
@@ -6147,10 +6681,10 @@
         <v>43830</v>
       </c>
       <c r="B227" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C227" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D227" s="5">
         <v>0.6597222222222222</v>
@@ -6161,10 +6695,10 @@
         <v>43830</v>
       </c>
       <c r="B228" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C228" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D228" s="5">
         <v>0.2152777777777778</v>
@@ -6175,10 +6709,10 @@
         <v>43830</v>
       </c>
       <c r="B229" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C229" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D229" s="5">
         <v>0.0763888888888889</v>
@@ -6189,10 +6723,10 @@
         <v>43830</v>
       </c>
       <c r="B230" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C230" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D230" s="5">
         <v>0.7430555555555556</v>
@@ -6203,10 +6737,10 @@
         <v>43830</v>
       </c>
       <c r="B231" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C231" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D231" s="5">
         <v>0.8125</v>
@@ -6217,10 +6751,10 @@
         <v>43830</v>
       </c>
       <c r="B232" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C232" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D232" s="5">
         <v>0.7013888888888888</v>
@@ -6231,10 +6765,10 @@
         <v>43830</v>
       </c>
       <c r="B233" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C233" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D233" s="5">
         <v>0.02083333333333333</v>
@@ -6245,10 +6779,10 @@
         <v>43830</v>
       </c>
       <c r="B234" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C234" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D234" s="5">
         <v>0.6319444444444444</v>
@@ -6259,10 +6793,10 @@
         <v>43830</v>
       </c>
       <c r="B235" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C235" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D235" s="5">
         <v>0.6041666666666666</v>
@@ -6273,10 +6807,10 @@
         <v>43830</v>
       </c>
       <c r="B236" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C236" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D236" s="5">
         <v>0.9236111111111112</v>
@@ -6287,10 +6821,10 @@
         <v>43830</v>
       </c>
       <c r="B237" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C237" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D237" s="5">
         <v>0.3402777777777778</v>
@@ -6301,10 +6835,10 @@
         <v>43830</v>
       </c>
       <c r="B238" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C238" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D238" s="5">
         <v>0.4236111111111111</v>
@@ -6315,10 +6849,10 @@
         <v>43830</v>
       </c>
       <c r="B239" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C239" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D239" s="5">
         <v>0.7708333333333334</v>
@@ -6329,10 +6863,10 @@
         <v>43830</v>
       </c>
       <c r="B240" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C240" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D240" s="5">
         <v>0.5902777777777778</v>
@@ -6343,10 +6877,10 @@
         <v>43830</v>
       </c>
       <c r="B241" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C241" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D241" s="5">
         <v>0.2986111111111111</v>
@@ -6357,10 +6891,10 @@
         <v>43830</v>
       </c>
       <c r="B242" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C242" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D242" s="5">
         <v>0.4930555555555556</v>
@@ -6371,10 +6905,10 @@
         <v>43830</v>
       </c>
       <c r="B243" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C243" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D243" s="5">
         <v>0.9097222222222222</v>
@@ -6385,10 +6919,10 @@
         <v>43830</v>
       </c>
       <c r="B244" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C244" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D244" s="5">
         <v>0.1875</v>
@@ -6399,10 +6933,10 @@
         <v>43830</v>
       </c>
       <c r="B245" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C245" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D245" s="5">
         <v>0.7847222222222222</v>
@@ -6413,10 +6947,10 @@
         <v>43830</v>
       </c>
       <c r="B246" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C246" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D246" s="5">
         <v>0.3819444444444444</v>
@@ -6427,10 +6961,10 @@
         <v>43830</v>
       </c>
       <c r="B247" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C247" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D247" s="5">
         <v>0.1458333333333333</v>
@@ -6441,10 +6975,10 @@
         <v>43830</v>
       </c>
       <c r="B248" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C248" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D248" s="5">
         <v>0.9652777777777778</v>
@@ -6455,10 +6989,10 @@
         <v>43830</v>
       </c>
       <c r="B249" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C249" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D249" s="5">
         <v>0.5763888888888888</v>
@@ -6469,10 +7003,10 @@
         <v>43830</v>
       </c>
       <c r="B250" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C250" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D250" s="5">
         <v>0.2013888888888889</v>
@@ -6483,10 +7017,10 @@
         <v>43830</v>
       </c>
       <c r="B251" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C251" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D251" s="5">
         <v>0.5069444444444444</v>
@@ -6497,10 +7031,10 @@
         <v>43830</v>
       </c>
       <c r="B252" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C252" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D252" s="5">
         <v>0.5347222222222222</v>
@@ -6511,10 +7045,10 @@
         <v>43830</v>
       </c>
       <c r="B253" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C253" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D253" s="5">
         <v>0.7152777777777778</v>
@@ -6525,10 +7059,10 @@
         <v>43830</v>
       </c>
       <c r="B254" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C254" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D254" s="5">
         <v>0.8958333333333334</v>
@@ -6539,10 +7073,10 @@
         <v>43830</v>
       </c>
       <c r="B255" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C255" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D255" s="5">
         <v>0.7986111111111112</v>
@@ -6553,10 +7087,10 @@
         <v>43830</v>
       </c>
       <c r="B256" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C256" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D256" s="5">
         <v>0.4375</v>
@@ -6567,10 +7101,10 @@
         <v>43830</v>
       </c>
       <c r="B257" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C257" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D257" s="5">
         <v>0.4097222222222222</v>
@@ -6581,10 +7115,10 @@
         <v>43830</v>
       </c>
       <c r="B258" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C258" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D258" s="5">
         <v>0.9375</v>
@@ -6595,10 +7129,10 @@
         <v>43830</v>
       </c>
       <c r="B259" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C259" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D259" s="5">
         <v>0.04861111111111111</v>
@@ -6609,10 +7143,10 @@
         <v>43830</v>
       </c>
       <c r="B260" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C260" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D260" s="5">
         <v>0.03472222222222222</v>
@@ -6623,10 +7157,10 @@
         <v>43830</v>
       </c>
       <c r="B261" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C261" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D261" s="5">
         <v>0.6180555555555556</v>
@@ -6637,10 +7171,10 @@
         <v>43830</v>
       </c>
       <c r="B262" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C262" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D262" s="5">
         <v>0.1041666666666667</v>
@@ -6651,10 +7185,10 @@
         <v>43830</v>
       </c>
       <c r="B263" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C263" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D263" s="5">
         <v>0.6458333333333334</v>
@@ -6665,10 +7199,10 @@
         <v>43830</v>
       </c>
       <c r="B264" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C264" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D264" s="5">
         <v>0.8402777777777778</v>
@@ -6679,10 +7213,10 @@
         <v>43830</v>
       </c>
       <c r="B265" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C265" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D265" s="5">
         <v>0.8819444444444444</v>
@@ -6693,10 +7227,10 @@
         <v>43830</v>
       </c>
       <c r="B266" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C266" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D266" s="5">
         <v>0.006944444444444444</v>
@@ -6707,10 +7241,10 @@
         <v>43830</v>
       </c>
       <c r="B267" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C267" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D267" s="5">
         <v>0.0625</v>
@@ -6721,10 +7255,10 @@
         <v>43830</v>
       </c>
       <c r="B268" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C268" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D268" s="5">
         <v>0.1319444444444444</v>
@@ -6735,10 +7269,10 @@
         <v>43830</v>
       </c>
       <c r="B269" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C269" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D269" s="5">
         <v>0.5208333333333334</v>
@@ -6749,10 +7283,10 @@
         <v>43830</v>
       </c>
       <c r="B270" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C270" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D270" s="5">
         <v>0.09027777777777778</v>
@@ -6763,10 +7297,10 @@
         <v>43830</v>
       </c>
       <c r="B271" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C271" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D271" s="5">
         <v>0.8680555555555556</v>
@@ -6777,10 +7311,10 @@
         <v>43830</v>
       </c>
       <c r="B272" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C272" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D272" s="5">
         <v>0.1180555555555556</v>
@@ -6791,10 +7325,10 @@
         <v>43830</v>
       </c>
       <c r="B273" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C273" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D273" s="5">
         <v>0.3125</v>
@@ -6805,10 +7339,10 @@
         <v>43830</v>
       </c>
       <c r="B274" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C274" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D274" s="5">
         <v>0.2847222222222222</v>
@@ -6819,10 +7353,10 @@
         <v>43830</v>
       </c>
       <c r="B275" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C275" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D275" s="5">
         <v>0.2430555555555556</v>
@@ -6833,10 +7367,10 @@
         <v>43830</v>
       </c>
       <c r="B276" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C276" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D276" s="5">
         <v>0.4513888888888889</v>
@@ -6847,10 +7381,10 @@
         <v>43830</v>
       </c>
       <c r="B277" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C277" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D277" s="5">
         <v>0.2291666666666667</v>
@@ -6861,10 +7395,10 @@
         <v>43830</v>
       </c>
       <c r="B278" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C278" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D278" s="5">
         <v>0.1736111111111111</v>
@@ -6875,10 +7409,10 @@
         <v>43830</v>
       </c>
       <c r="B279" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C279" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D279" s="5">
         <v>0.7569444444444444</v>
@@ -6889,10 +7423,10 @@
         <v>43830</v>
       </c>
       <c r="B280" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C280" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D280" s="5">
         <v>0.9791666666666666</v>
@@ -6903,10 +7437,10 @@
         <v>43830</v>
       </c>
       <c r="B281" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C281" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D281" s="5">
         <v>0.8541666666666666</v>
@@ -6917,10 +7451,10 @@
         <v>43830</v>
       </c>
       <c r="B282" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C282" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D282" s="5">
         <v>0.6875</v>
@@ -6931,10 +7465,10 @@
         <v>43830</v>
       </c>
       <c r="B283" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C283" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D283" s="5">
         <v>0.3958333333333333</v>
@@ -6945,10 +7479,10 @@
         <v>43830</v>
       </c>
       <c r="B284" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C284" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D284" s="5">
         <v>0.6736111111111112</v>
@@ -6959,10 +7493,10 @@
         <v>43830</v>
       </c>
       <c r="B285" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C285" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D285" s="5">
         <v>0.5486111111111112</v>
@@ -6973,10 +7507,10 @@
         <v>43830</v>
       </c>
       <c r="B286" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C286" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D286" s="5">
         <v>0.1597222222222222</v>
@@ -6987,10 +7521,10 @@
         <v>43830</v>
       </c>
       <c r="B287" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C287" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D287" s="5">
         <v>0.2569444444444444</v>
@@ -7001,10 +7535,10 @@
         <v>43830</v>
       </c>
       <c r="B288" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C288" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D288" s="5">
         <v>0.3680555555555556</v>
@@ -7015,10 +7549,10 @@
         <v>43830</v>
       </c>
       <c r="B289" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C289" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D289" s="5">
         <v>0.4652777777777778</v>
@@ -7029,10 +7563,10 @@
         <v>43830</v>
       </c>
       <c r="B290" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C290" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D290" s="5">
         <v>0.7291666666666666</v>
@@ -7043,10 +7577,10 @@
         <v>43830</v>
       </c>
       <c r="B291" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C291" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D291" s="5">
         <v>0.6041666666666666</v>
@@ -7057,10 +7591,10 @@
         <v>43830</v>
       </c>
       <c r="B292" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C292" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D292" s="5">
         <v>0.9930555555555556</v>
@@ -7071,10 +7605,10 @@
         <v>43830</v>
       </c>
       <c r="B293" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C293" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D293" s="5">
         <v>0.0625</v>
@@ -7085,10 +7619,10 @@
         <v>43830</v>
       </c>
       <c r="B294" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C294" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D294" s="5">
         <v>0.1041666666666667</v>
@@ -7099,10 +7633,10 @@
         <v>43830</v>
       </c>
       <c r="B295" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C295" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D295" s="5">
         <v>0.3402777777777778</v>
@@ -7113,10 +7647,10 @@
         <v>43830</v>
       </c>
       <c r="B296" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C296" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D296" s="5">
         <v>0.8680555555555556</v>
@@ -7127,10 +7661,10 @@
         <v>43830</v>
       </c>
       <c r="B297" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C297" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D297" s="5">
         <v>0.006944444444444444</v>
@@ -7141,10 +7675,10 @@
         <v>43830</v>
       </c>
       <c r="B298" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C298" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D298" s="5">
         <v>0.5625</v>
@@ -7155,10 +7689,10 @@
         <v>43830</v>
       </c>
       <c r="B299" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C299" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D299" s="5">
         <v>0.03472222222222222</v>
@@ -7169,10 +7703,10 @@
         <v>43830</v>
       </c>
       <c r="B300" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C300" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D300" s="5">
         <v>0.1597222222222222</v>
@@ -7183,10 +7717,10 @@
         <v>43830</v>
       </c>
       <c r="B301" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C301" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D301" s="5">
         <v>0.8402777777777778</v>
@@ -7197,10 +7731,10 @@
         <v>43830</v>
       </c>
       <c r="B302" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C302" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D302" s="5">
         <v>0.8541666666666666</v>
@@ -7211,10 +7745,10 @@
         <v>43830</v>
       </c>
       <c r="B303" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C303" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D303" s="5">
         <v>0.2430555555555556</v>
@@ -7225,10 +7759,10 @@
         <v>43830</v>
       </c>
       <c r="B304" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C304" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D304" s="5">
         <v>0.2291666666666667</v>
@@ -7239,10 +7773,10 @@
         <v>43830</v>
       </c>
       <c r="B305" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C305" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D305" s="5">
         <v>0.7847222222222222</v>
@@ -7253,10 +7787,10 @@
         <v>43830</v>
       </c>
       <c r="B306" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C306" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D306" s="5">
         <v>0.4791666666666667</v>
@@ -7267,10 +7801,10 @@
         <v>43830</v>
       </c>
       <c r="B307" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C307" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D307" s="5">
         <v>0.5208333333333334</v>
@@ -7281,10 +7815,10 @@
         <v>43830</v>
       </c>
       <c r="B308" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C308" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D308" s="5">
         <v>0.3819444444444444</v>
@@ -7295,10 +7829,10 @@
         <v>43830</v>
       </c>
       <c r="B309" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C309" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D309" s="5">
         <v>0.5486111111111112</v>
@@ -7309,10 +7843,10 @@
         <v>43830</v>
       </c>
       <c r="B310" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C310" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D310" s="5">
         <v>0.02083333333333333</v>
@@ -7323,10 +7857,10 @@
         <v>43830</v>
       </c>
       <c r="B311" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C311" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D311" s="5">
         <v>0.9652777777777778</v>
@@ -7337,10 +7871,10 @@
         <v>43830</v>
       </c>
       <c r="B312" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C312" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D312" s="5">
         <v>0.6736111111111112</v>
@@ -7351,10 +7885,10 @@
         <v>43830</v>
       </c>
       <c r="B313" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C313" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D313" s="5">
         <v>0.7708333333333334</v>
@@ -7365,10 +7899,10 @@
         <v>43830</v>
       </c>
       <c r="B314" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C314" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D314" s="5">
         <v>0.7152777777777778</v>
@@ -7379,10 +7913,10 @@
         <v>43830</v>
       </c>
       <c r="B315" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C315" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D315" s="5">
         <v>0.8263888888888888</v>
@@ -7393,10 +7927,10 @@
         <v>43830</v>
       </c>
       <c r="B316" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C316" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D316" s="5">
         <v>0.5347222222222222</v>
@@ -7407,10 +7941,10 @@
         <v>43830</v>
       </c>
       <c r="B317" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C317" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D317" s="5">
         <v>0.9513888888888888</v>
@@ -7421,10 +7955,10 @@
         <v>43830</v>
       </c>
       <c r="B318" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C318" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D318" s="5">
         <v>0.8125</v>
@@ -7435,10 +7969,10 @@
         <v>43830</v>
       </c>
       <c r="B319" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C319" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D319" s="5">
         <v>0.6319444444444444</v>
@@ -7449,10 +7983,10 @@
         <v>43830</v>
       </c>
       <c r="B320" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C320" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D320" s="5">
         <v>0.4930555555555556</v>
@@ -7463,10 +7997,10 @@
         <v>43830</v>
       </c>
       <c r="B321" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C321" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D321" s="5">
         <v>0.9236111111111112</v>
@@ -7477,10 +8011,10 @@
         <v>43830</v>
       </c>
       <c r="B322" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C322" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D322" s="5">
         <v>0.2986111111111111</v>
@@ -7491,10 +8025,10 @@
         <v>43830</v>
       </c>
       <c r="B323" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C323" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D323" s="5">
         <v>0.1180555555555556</v>
@@ -7505,10 +8039,10 @@
         <v>43830</v>
       </c>
       <c r="B324" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C324" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D324" s="5">
         <v>0.2152777777777778</v>
@@ -7519,10 +8053,10 @@
         <v>43830</v>
       </c>
       <c r="B325" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C325" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D325" s="5">
         <v>0.6875</v>
@@ -7533,10 +8067,10 @@
         <v>43830</v>
       </c>
       <c r="B326" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C326" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D326" s="5">
         <v>0.6458333333333334</v>
@@ -7547,10 +8081,10 @@
         <v>43830</v>
       </c>
       <c r="B327" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C327" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D327" s="5">
         <v>0.1319444444444444</v>
@@ -7561,10 +8095,10 @@
         <v>43830</v>
       </c>
       <c r="B328" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C328" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D328" s="5">
         <v>0.0763888888888889</v>
@@ -7575,10 +8109,10 @@
         <v>43830</v>
       </c>
       <c r="B329" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C329" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D329" s="5">
         <v>0.7986111111111112</v>
@@ -7589,10 +8123,10 @@
         <v>43830</v>
       </c>
       <c r="B330" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C330" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D330" s="5">
         <v>0.8819444444444444</v>
@@ -7603,10 +8137,10 @@
         <v>43830</v>
       </c>
       <c r="B331" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C331" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D331" s="5">
         <v>0.4097222222222222</v>
@@ -7617,10 +8151,10 @@
         <v>43830</v>
       </c>
       <c r="B332" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C332" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D332" s="5">
         <v>0.4236111111111111</v>
@@ -7631,10 +8165,10 @@
         <v>43830</v>
       </c>
       <c r="B333" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C333" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D333" s="5">
         <v>0.6180555555555556</v>
@@ -7645,10 +8179,10 @@
         <v>43830</v>
       </c>
       <c r="B334" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C334" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D334" s="5">
         <v>0.1458333333333333</v>
@@ -7659,10 +8193,10 @@
         <v>43830</v>
       </c>
       <c r="B335" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C335" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D335" s="5">
         <v>0.7569444444444444</v>
@@ -7673,10 +8207,10 @@
         <v>43830</v>
       </c>
       <c r="B336" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C336" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D336" s="5">
         <v>0.1736111111111111</v>
@@ -7687,10 +8221,10 @@
         <v>43830</v>
       </c>
       <c r="B337" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C337" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D337" s="5">
         <v>0.2569444444444444</v>
@@ -7701,10 +8235,10 @@
         <v>43830</v>
       </c>
       <c r="B338" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C338" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D338" s="5">
         <v>0.7430555555555556</v>
@@ -7715,10 +8249,10 @@
         <v>43830</v>
       </c>
       <c r="B339" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C339" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D339" s="5">
         <v>0.4513888888888889</v>
@@ -7729,10 +8263,10 @@
         <v>43830</v>
       </c>
       <c r="B340" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C340" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D340" s="5">
         <v>0.2013888888888889</v>
@@ -7743,10 +8277,10 @@
         <v>43830</v>
       </c>
       <c r="B341" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C341" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D341" s="5">
         <v>0.3680555555555556</v>
@@ -7757,10 +8291,10 @@
         <v>43830</v>
       </c>
       <c r="B342" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C342" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D342" s="5">
         <v>0.8958333333333334</v>
@@ -7771,10 +8305,10 @@
         <v>43830</v>
       </c>
       <c r="B343" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C343" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D343" s="5">
         <v>0.9097222222222222</v>
@@ -7785,10 +8319,10 @@
         <v>43830</v>
       </c>
       <c r="B344" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C344" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D344" s="5">
         <v>0.9791666666666666</v>
@@ -7799,10 +8333,10 @@
         <v>43830</v>
       </c>
       <c r="B345" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C345" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D345" s="5">
         <v>0.3125</v>
@@ -7813,10 +8347,10 @@
         <v>43830</v>
       </c>
       <c r="B346" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C346" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D346" s="5">
         <v>0.9375</v>
@@ -7827,10 +8361,10 @@
         <v>43830</v>
       </c>
       <c r="B347" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C347" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D347" s="5">
         <v>0.4375</v>
@@ -7841,10 +8375,10 @@
         <v>43830</v>
       </c>
       <c r="B348" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C348" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D348" s="5">
         <v>0.3263888888888889</v>
@@ -7855,10 +8389,10 @@
         <v>43830</v>
       </c>
       <c r="B349" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C349" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D349" s="5">
         <v>0.1875</v>
@@ -7869,10 +8403,10 @@
         <v>43830</v>
       </c>
       <c r="B350" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C350" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D350" s="5">
         <v>0.5763888888888888</v>
@@ -7883,10 +8417,10 @@
         <v>43830</v>
       </c>
       <c r="B351" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C351" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D351" s="5">
         <v>0.5069444444444444</v>
@@ -7897,10 +8431,10 @@
         <v>43830</v>
       </c>
       <c r="B352" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C352" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D352" s="5">
         <v>0.5902777777777778</v>
@@ -7911,10 +8445,10 @@
         <v>43830</v>
       </c>
       <c r="B353" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C353" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D353" s="5">
         <v>0.2708333333333333</v>
@@ -7925,10 +8459,10 @@
         <v>43830</v>
       </c>
       <c r="B354" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C354" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D354" s="5">
         <v>0.4652777777777778</v>
@@ -7939,10 +8473,10 @@
         <v>43830</v>
       </c>
       <c r="B355" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C355" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D355" s="5">
         <v>0.7013888888888888</v>
@@ -7953,10 +8487,10 @@
         <v>43830</v>
       </c>
       <c r="B356" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C356" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D356" s="5">
         <v>0.2847222222222222</v>
@@ -7967,10 +8501,10 @@
         <v>43830</v>
       </c>
       <c r="B357" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C357" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D357" s="5">
         <v>0.04861111111111111</v>
@@ -7981,10 +8515,10 @@
         <v>43830</v>
       </c>
       <c r="B358" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C358" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D358" s="5">
         <v>0.09027777777777778</v>
@@ -7995,10 +8529,10 @@
         <v>43830</v>
       </c>
       <c r="B359" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C359" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D359" s="5">
         <v>0.3541666666666667</v>
@@ -8009,10 +8543,10 @@
         <v>43830</v>
       </c>
       <c r="B360" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C360" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D360" s="5">
         <v>0.6597222222222222</v>
@@ -8023,10 +8557,10 @@
         <v>43830</v>
       </c>
       <c r="B361" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C361" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D361" s="5">
         <v>0.3958333333333333</v>
@@ -8037,10 +8571,10 @@
         <v>43830</v>
       </c>
       <c r="B362" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C362" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D362" s="5">
         <v>0.9236111111111112</v>
@@ -8051,10 +8585,10 @@
         <v>43830</v>
       </c>
       <c r="B363" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C363" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D363" s="5">
         <v>0.9652777777777778</v>
@@ -8065,10 +8599,10 @@
         <v>43830</v>
       </c>
       <c r="B364" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C364" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D364" s="5">
         <v>0.9097222222222222</v>
@@ -8079,10 +8613,10 @@
         <v>43830</v>
       </c>
       <c r="B365" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C365" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D365" s="5">
         <v>0.4652777777777778</v>
@@ -8093,10 +8627,10 @@
         <v>43830</v>
       </c>
       <c r="B366" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C366" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D366" s="5">
         <v>0.2430555555555556</v>
@@ -8107,10 +8641,10 @@
         <v>43830</v>
       </c>
       <c r="B367" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C367" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D367" s="5">
         <v>0.2013888888888889</v>
@@ -8121,10 +8655,10 @@
         <v>43830</v>
       </c>
       <c r="B368" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C368" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D368" s="5">
         <v>0.6736111111111112</v>
@@ -8135,10 +8669,10 @@
         <v>43830</v>
       </c>
       <c r="B369" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C369" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D369" s="5">
         <v>0.02083333333333333</v>
@@ -8149,10 +8683,10 @@
         <v>43830</v>
       </c>
       <c r="B370" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C370" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D370" s="5">
         <v>0.3680555555555556</v>
@@ -8163,10 +8697,10 @@
         <v>43830</v>
       </c>
       <c r="B371" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C371" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D371" s="5">
         <v>0.1875</v>
@@ -8177,10 +8711,10 @@
         <v>43830</v>
       </c>
       <c r="B372" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C372" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D372" s="5">
         <v>0.1041666666666667</v>
@@ -8191,10 +8725,10 @@
         <v>43830</v>
       </c>
       <c r="B373" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C373" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D373" s="5">
         <v>0.7013888888888888</v>
@@ -8205,10 +8739,10 @@
         <v>43830</v>
       </c>
       <c r="B374" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C374" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D374" s="5">
         <v>0.7569444444444444</v>
@@ -8219,10 +8753,10 @@
         <v>43830</v>
       </c>
       <c r="B375" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C375" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D375" s="5">
         <v>0.3402777777777778</v>
@@ -8233,10 +8767,10 @@
         <v>43830</v>
       </c>
       <c r="B376" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C376" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D376" s="5">
         <v>0.2152777777777778</v>
@@ -8247,10 +8781,10 @@
         <v>43830</v>
       </c>
       <c r="B377" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C377" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D377" s="5">
         <v>0.5347222222222222</v>
@@ -8261,10 +8795,10 @@
         <v>43830</v>
       </c>
       <c r="B378" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C378" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D378" s="5">
         <v>0.7986111111111112</v>
@@ -8275,10 +8809,10 @@
         <v>43830</v>
       </c>
       <c r="B379" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C379" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D379" s="5">
         <v>0.4375</v>
@@ -8289,10 +8823,10 @@
         <v>43830</v>
       </c>
       <c r="B380" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C380" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D380" s="5">
         <v>0.2986111111111111</v>
@@ -8303,10 +8837,10 @@
         <v>43830</v>
       </c>
       <c r="B381" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C381" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D381" s="5">
         <v>0.2847222222222222</v>
@@ -8317,10 +8851,10 @@
         <v>43830</v>
       </c>
       <c r="B382" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C382" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D382" s="5">
         <v>0.006944444444444444</v>
@@ -8331,10 +8865,10 @@
         <v>43830</v>
       </c>
       <c r="B383" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C383" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D383" s="5">
         <v>0.7847222222222222</v>
@@ -8345,10 +8879,10 @@
         <v>43830</v>
       </c>
       <c r="B384" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C384" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D384" s="5">
         <v>0.3958333333333333</v>
@@ -8359,10 +8893,10 @@
         <v>43830</v>
       </c>
       <c r="B385" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C385" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D385" s="5">
         <v>0.8125</v>
@@ -8373,10 +8907,10 @@
         <v>43830</v>
       </c>
       <c r="B386" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C386" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D386" s="5">
         <v>0.7708333333333334</v>
@@ -8387,10 +8921,10 @@
         <v>43830</v>
       </c>
       <c r="B387" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C387" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D387" s="5">
         <v>0.9791666666666666</v>
@@ -8401,10 +8935,10 @@
         <v>43830</v>
       </c>
       <c r="B388" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C388" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D388" s="5">
         <v>0.6041666666666666</v>
@@ -8415,10 +8949,10 @@
         <v>43830</v>
       </c>
       <c r="B389" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C389" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D389" s="5">
         <v>0.7430555555555556</v>
@@ -8429,10 +8963,10 @@
         <v>43830</v>
       </c>
       <c r="B390" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C390" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D390" s="5">
         <v>0.5625</v>
@@ -8443,10 +8977,10 @@
         <v>43830</v>
       </c>
       <c r="B391" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C391" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D391" s="5">
         <v>0.4791666666666667</v>
@@ -8457,10 +8991,10 @@
         <v>43830</v>
       </c>
       <c r="B392" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C392" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D392" s="5">
         <v>0.2291666666666667</v>
@@ -8471,10 +9005,10 @@
         <v>43830</v>
       </c>
       <c r="B393" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C393" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D393" s="5">
         <v>0.8263888888888888</v>
@@ -8485,10 +9019,10 @@
         <v>43830</v>
       </c>
       <c r="B394" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C394" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D394" s="5">
         <v>0.5208333333333334</v>
@@ -8499,10 +9033,10 @@
         <v>43830</v>
       </c>
       <c r="B395" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C395" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D395" s="5">
         <v>0.1180555555555556</v>
@@ -8513,10 +9047,10 @@
         <v>43830</v>
       </c>
       <c r="B396" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C396" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D396" s="5">
         <v>0.0625</v>
@@ -8527,10 +9061,10 @@
         <v>43830</v>
       </c>
       <c r="B397" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C397" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D397" s="5">
         <v>0.7152777777777778</v>
@@ -8541,10 +9075,10 @@
         <v>43830</v>
       </c>
       <c r="B398" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C398" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D398" s="5">
         <v>0.4513888888888889</v>
@@ -8555,10 +9089,10 @@
         <v>43830</v>
       </c>
       <c r="B399" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C399" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D399" s="5">
         <v>0.2708333333333333</v>
@@ -8569,10 +9103,10 @@
         <v>43830</v>
       </c>
       <c r="B400" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C400" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D400" s="5">
         <v>0.1736111111111111</v>
@@ -8583,10 +9117,10 @@
         <v>43830</v>
       </c>
       <c r="B401" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C401" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D401" s="5">
         <v>0.4236111111111111</v>
@@ -8597,10 +9131,10 @@
         <v>43830</v>
       </c>
       <c r="B402" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C402" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D402" s="5">
         <v>0.8680555555555556</v>
@@ -8611,10 +9145,10 @@
         <v>43830</v>
       </c>
       <c r="B403" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C403" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D403" s="5">
         <v>0.3263888888888889</v>
@@ -8625,10 +9159,10 @@
         <v>43830</v>
       </c>
       <c r="B404" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C404" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D404" s="5">
         <v>0.3819444444444444</v>
@@ -8639,10 +9173,10 @@
         <v>43830</v>
       </c>
       <c r="B405" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C405" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D405" s="5">
         <v>0.6180555555555556</v>
@@ -8653,10 +9187,10 @@
         <v>43830</v>
       </c>
       <c r="B406" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C406" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D406" s="5">
         <v>0.5763888888888888</v>
@@ -8667,10 +9201,10 @@
         <v>43830</v>
       </c>
       <c r="B407" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C407" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D407" s="5">
         <v>0.5902777777777778</v>
@@ -8681,10 +9215,10 @@
         <v>43830</v>
       </c>
       <c r="B408" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C408" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D408" s="5">
         <v>0.1597222222222222</v>
@@ -8695,10 +9229,10 @@
         <v>43830</v>
       </c>
       <c r="B409" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C409" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D409" s="5">
         <v>0.6875</v>
@@ -8709,10 +9243,10 @@
         <v>43830</v>
       </c>
       <c r="B410" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C410" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D410" s="5">
         <v>0.9375</v>
@@ -8723,10 +9257,10 @@
         <v>43830</v>
       </c>
       <c r="B411" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C411" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D411" s="5">
         <v>0.6319444444444444</v>
@@ -8737,10 +9271,10 @@
         <v>43830</v>
       </c>
       <c r="B412" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C412" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D412" s="5">
         <v>0.03472222222222222</v>
@@ -8751,10 +9285,10 @@
         <v>43830</v>
       </c>
       <c r="B413" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C413" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D413" s="5">
         <v>0.3125</v>
@@ -8765,10 +9299,10 @@
         <v>43830</v>
       </c>
       <c r="B414" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C414" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D414" s="5">
         <v>0.8819444444444444</v>
@@ -8779,10 +9313,10 @@
         <v>43830</v>
       </c>
       <c r="B415" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C415" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D415" s="5">
         <v>0.9513888888888888</v>
@@ -8793,10 +9327,10 @@
         <v>43830</v>
       </c>
       <c r="B416" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C416" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D416" s="5">
         <v>0.9930555555555556</v>
@@ -8807,10 +9341,10 @@
         <v>43830</v>
       </c>
       <c r="B417" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C417" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D417" s="5">
         <v>0.09027777777777778</v>
@@ -8821,10 +9355,10 @@
         <v>43830</v>
       </c>
       <c r="B418" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C418" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D418" s="5">
         <v>0.8958333333333334</v>
@@ -8835,10 +9369,10 @@
         <v>43830</v>
       </c>
       <c r="B419" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C419" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D419" s="5">
         <v>0.2569444444444444</v>
@@ -8849,10 +9383,10 @@
         <v>43830</v>
       </c>
       <c r="B420" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C420" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D420" s="5">
         <v>0.1319444444444444</v>
@@ -8863,10 +9397,10 @@
         <v>43830</v>
       </c>
       <c r="B421" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C421" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D421" s="5">
         <v>0.1458333333333333</v>
@@ -8877,10 +9411,10 @@
         <v>43830</v>
       </c>
       <c r="B422" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C422" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D422" s="5">
         <v>0.8402777777777778</v>
@@ -8891,10 +9425,10 @@
         <v>43830</v>
       </c>
       <c r="B423" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C423" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D423" s="5">
         <v>0.7291666666666666</v>
@@ -8905,10 +9439,10 @@
         <v>43830</v>
       </c>
       <c r="B424" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C424" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D424" s="5">
         <v>0.5486111111111112</v>
@@ -8919,10 +9453,10 @@
         <v>43830</v>
       </c>
       <c r="B425" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C425" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D425" s="5">
         <v>0.3541666666666667</v>
@@ -8933,10 +9467,10 @@
         <v>43830</v>
       </c>
       <c r="B426" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C426" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D426" s="5">
         <v>0.4930555555555556</v>
@@ -8947,10 +9481,10 @@
         <v>43830</v>
       </c>
       <c r="B427" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C427" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D427" s="5">
         <v>0.8541666666666666</v>
@@ -8961,10 +9495,10 @@
         <v>43830</v>
       </c>
       <c r="B428" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C428" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D428" s="5">
         <v>0.6458333333333334</v>
@@ -8975,10 +9509,10 @@
         <v>43830</v>
       </c>
       <c r="B429" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C429" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D429" s="5">
         <v>0.5069444444444444</v>
@@ -8989,10 +9523,10 @@
         <v>43830</v>
       </c>
       <c r="B430" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C430" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D430" s="5">
         <v>0.0763888888888889</v>
@@ -9003,10 +9537,10 @@
         <v>43830</v>
       </c>
       <c r="B431" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C431" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D431" s="5">
         <v>0.4097222222222222</v>
@@ -9017,10 +9551,10 @@
         <v>43830</v>
       </c>
       <c r="B432" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C432" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D432" s="5">
         <v>0.6597222222222222</v>
@@ -9031,10 +9565,10 @@
         <v>43830</v>
       </c>
       <c r="B433" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C433" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D433" s="5">
         <v>0.04861111111111111</v>
@@ -9045,10 +9579,10 @@
         <v>43830</v>
       </c>
       <c r="B434" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C434" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D434" s="5">
         <v>0.7291666666666666</v>
@@ -9059,10 +9593,10 @@
         <v>43830</v>
       </c>
       <c r="B435" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C435" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D435" s="5">
         <v>0.7569444444444444</v>
@@ -9073,10 +9607,10 @@
         <v>43830</v>
       </c>
       <c r="B436" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C436" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D436" s="5">
         <v>0.5902777777777778</v>
@@ -9087,10 +9621,10 @@
         <v>43830</v>
       </c>
       <c r="B437" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C437" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D437" s="5">
         <v>0.6180555555555556</v>
@@ -9101,10 +9635,10 @@
         <v>43830</v>
       </c>
       <c r="B438" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C438" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D438" s="5">
         <v>0.5069444444444444</v>
@@ -9115,10 +9649,10 @@
         <v>43830</v>
       </c>
       <c r="B439" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C439" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D439" s="5">
         <v>0.3958333333333333</v>
@@ -9129,10 +9663,10 @@
         <v>43830</v>
       </c>
       <c r="B440" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C440" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D440" s="5">
         <v>0.8541666666666666</v>
@@ -9143,10 +9677,10 @@
         <v>43830</v>
       </c>
       <c r="B441" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C441" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D441" s="5">
         <v>0.3125</v>
@@ -9157,10 +9691,10 @@
         <v>43830</v>
       </c>
       <c r="B442" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C442" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D442" s="5">
         <v>0.8958333333333334</v>
@@ -9171,10 +9705,10 @@
         <v>43830</v>
       </c>
       <c r="B443" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C443" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D443" s="5">
         <v>0.2152777777777778</v>
@@ -9185,10 +9719,10 @@
         <v>43830</v>
       </c>
       <c r="B444" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C444" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D444" s="5">
         <v>0.9375</v>
@@ -9199,10 +9733,10 @@
         <v>43830</v>
       </c>
       <c r="B445" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C445" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D445" s="5">
         <v>0.4513888888888889</v>
@@ -9213,10 +9747,10 @@
         <v>43830</v>
       </c>
       <c r="B446" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C446" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D446" s="5">
         <v>0.3402777777777778</v>
@@ -9227,10 +9761,10 @@
         <v>43830</v>
       </c>
       <c r="B447" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C447" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D447" s="5">
         <v>0.2291666666666667</v>
@@ -9241,10 +9775,10 @@
         <v>43830</v>
       </c>
       <c r="B448" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C448" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D448" s="5">
         <v>0.5625</v>
@@ -9255,10 +9789,10 @@
         <v>43830</v>
       </c>
       <c r="B449" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C449" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D449" s="5">
         <v>0.8125</v>
@@ -9269,10 +9803,10 @@
         <v>43830</v>
       </c>
       <c r="B450" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C450" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D450" s="5">
         <v>0.9236111111111112</v>
@@ -9283,10 +9817,10 @@
         <v>43830</v>
       </c>
       <c r="B451" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C451" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D451" s="5">
         <v>0.4791666666666667</v>
@@ -9297,10 +9831,10 @@
         <v>43830</v>
       </c>
       <c r="B452" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C452" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D452" s="5">
         <v>0.9097222222222222</v>
@@ -9311,10 +9845,10 @@
         <v>43830</v>
       </c>
       <c r="B453" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C453" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D453" s="5">
         <v>0.5486111111111112</v>
@@ -9325,10 +9859,10 @@
         <v>43830</v>
       </c>
       <c r="B454" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C454" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D454" s="5">
         <v>0.2986111111111111</v>
@@ -9339,10 +9873,10 @@
         <v>43830</v>
       </c>
       <c r="B455" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C455" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D455" s="5">
         <v>0.4375</v>
@@ -9353,10 +9887,10 @@
         <v>43830</v>
       </c>
       <c r="B456" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C456" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D456" s="5">
         <v>0.8680555555555556</v>
@@ -9367,10 +9901,10 @@
         <v>43830</v>
       </c>
       <c r="B457" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C457" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D457" s="5">
         <v>0.1041666666666667</v>
@@ -9381,10 +9915,10 @@
         <v>43830</v>
       </c>
       <c r="B458" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C458" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D458" s="5">
         <v>0.4930555555555556</v>
@@ -9395,10 +9929,10 @@
         <v>43830</v>
       </c>
       <c r="B459" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C459" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D459" s="5">
         <v>0.7986111111111112</v>
@@ -9409,10 +9943,10 @@
         <v>43830</v>
       </c>
       <c r="B460" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C460" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D460" s="5">
         <v>0.7430555555555556</v>
@@ -9423,10 +9957,10 @@
         <v>43830</v>
       </c>
       <c r="B461" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C461" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D461" s="5">
         <v>0.6736111111111112</v>
@@ -9437,10 +9971,10 @@
         <v>43830</v>
       </c>
       <c r="B462" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C462" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D462" s="5">
         <v>0.5208333333333334</v>
@@ -9451,10 +9985,10 @@
         <v>43830</v>
       </c>
       <c r="B463" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C463" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D463" s="5">
         <v>0.1319444444444444</v>
@@ -9465,10 +9999,10 @@
         <v>43830</v>
       </c>
       <c r="B464" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C464" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D464" s="5">
         <v>0.2430555555555556</v>
@@ -9479,10 +10013,10 @@
         <v>43830</v>
       </c>
       <c r="B465" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C465" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D465" s="5">
         <v>0.3541666666666667</v>
@@ -9493,10 +10027,10 @@
         <v>43830</v>
       </c>
       <c r="B466" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C466" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D466" s="5">
         <v>0.2847222222222222</v>
@@ -9507,10 +10041,10 @@
         <v>43830</v>
       </c>
       <c r="B467" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C467" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D467" s="5">
         <v>0.4652777777777778</v>
@@ -9521,10 +10055,10 @@
         <v>43830</v>
       </c>
       <c r="B468" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C468" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D468" s="5">
         <v>0.2708333333333333</v>
@@ -9535,10 +10069,10 @@
         <v>43830</v>
       </c>
       <c r="B469" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C469" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D469" s="5">
         <v>0.6319444444444444</v>
@@ -9549,10 +10083,10 @@
         <v>43830</v>
       </c>
       <c r="B470" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C470" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D470" s="5">
         <v>0.6875</v>
@@ -9563,10 +10097,10 @@
         <v>43830</v>
       </c>
       <c r="B471" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C471" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D471" s="5">
         <v>0.1736111111111111</v>
@@ -9577,10 +10111,10 @@
         <v>43830</v>
       </c>
       <c r="B472" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C472" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D472" s="5">
         <v>0.03472222222222222</v>
@@ -9591,10 +10125,10 @@
         <v>43830</v>
       </c>
       <c r="B473" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C473" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D473" s="5">
         <v>0.3680555555555556</v>
@@ -9605,10 +10139,10 @@
         <v>43830</v>
       </c>
       <c r="B474" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C474" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D474" s="5">
         <v>0.9930555555555556</v>
@@ -9619,10 +10153,10 @@
         <v>43830</v>
       </c>
       <c r="B475" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C475" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D475" s="5">
         <v>0.3819444444444444</v>
@@ -9633,10 +10167,10 @@
         <v>43830</v>
       </c>
       <c r="B476" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C476" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D476" s="5">
         <v>0.6041666666666666</v>
@@ -9647,10 +10181,10 @@
         <v>43830</v>
       </c>
       <c r="B477" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C477" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D477" s="5">
         <v>0.2013888888888889</v>
@@ -9661,10 +10195,10 @@
         <v>43830</v>
       </c>
       <c r="B478" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C478" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D478" s="5">
         <v>0.9513888888888888</v>
@@ -9675,10 +10209,10 @@
         <v>43830</v>
       </c>
       <c r="B479" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C479" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D479" s="5">
         <v>0.3263888888888889</v>
@@ -9689,10 +10223,10 @@
         <v>43830</v>
       </c>
       <c r="B480" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C480" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D480" s="5">
         <v>0.4236111111111111</v>
@@ -9703,10 +10237,10 @@
         <v>43830</v>
       </c>
       <c r="B481" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C481" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D481" s="5">
         <v>0.7152777777777778</v>
@@ -9717,10 +10251,10 @@
         <v>43830</v>
       </c>
       <c r="B482" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C482" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D482" s="5">
         <v>0.5763888888888888</v>
@@ -9731,10 +10265,10 @@
         <v>43830</v>
       </c>
       <c r="B483" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C483" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D483" s="5">
         <v>0.7847222222222222</v>
@@ -9745,10 +10279,10 @@
         <v>43830</v>
       </c>
       <c r="B484" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C484" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D484" s="5">
         <v>0.8263888888888888</v>
@@ -9759,10 +10293,10 @@
         <v>43830</v>
       </c>
       <c r="B485" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C485" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D485" s="5">
         <v>0.7708333333333334</v>
@@ -9773,10 +10307,10 @@
         <v>43830</v>
       </c>
       <c r="B486" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C486" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D486" s="5">
         <v>0.2569444444444444</v>
@@ -9787,10 +10321,10 @@
         <v>43830</v>
       </c>
       <c r="B487" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C487" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D487" s="5">
         <v>0.7013888888888888</v>
@@ -9801,10 +10335,10 @@
         <v>43830</v>
       </c>
       <c r="B488" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C488" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D488" s="5">
         <v>0.0625</v>
@@ -9815,10 +10349,10 @@
         <v>43830</v>
       </c>
       <c r="B489" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C489" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D489" s="5">
         <v>0.6458333333333334</v>
@@ -9829,10 +10363,10 @@
         <v>43830</v>
       </c>
       <c r="B490" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C490" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D490" s="5">
         <v>0.8819444444444444</v>
@@ -9843,10 +10377,10 @@
         <v>43830</v>
       </c>
       <c r="B491" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C491" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D491" s="5">
         <v>0.1597222222222222</v>
@@ -9857,10 +10391,10 @@
         <v>43830</v>
       </c>
       <c r="B492" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C492" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D492" s="5">
         <v>0.04861111111111111</v>
@@ -9871,10 +10405,10 @@
         <v>43830</v>
       </c>
       <c r="B493" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C493" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D493" s="5">
         <v>0.8402777777777778</v>
@@ -9885,10 +10419,10 @@
         <v>43830</v>
       </c>
       <c r="B494" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C494" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D494" s="5">
         <v>0.1458333333333333</v>
@@ -9899,10 +10433,10 @@
         <v>43830</v>
       </c>
       <c r="B495" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C495" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D495" s="5">
         <v>0.1180555555555556</v>
@@ -9913,10 +10447,10 @@
         <v>43830</v>
       </c>
       <c r="B496" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C496" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D496" s="5">
         <v>0.9791666666666666</v>
@@ -9927,10 +10461,10 @@
         <v>43830</v>
       </c>
       <c r="B497" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C497" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D497" s="5">
         <v>0.09027777777777778</v>
@@ -9941,10 +10475,10 @@
         <v>43830</v>
       </c>
       <c r="B498" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C498" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D498" s="5">
         <v>0.0763888888888889</v>
@@ -9955,10 +10489,10 @@
         <v>43830</v>
       </c>
       <c r="B499" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C499" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D499" s="5">
         <v>0.5347222222222222</v>
@@ -9969,10 +10503,10 @@
         <v>43830</v>
       </c>
       <c r="B500" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C500" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D500" s="5">
         <v>0.02083333333333333</v>
@@ -9983,10 +10517,10 @@
         <v>43830</v>
       </c>
       <c r="B501" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C501" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D501" s="5">
         <v>0.9652777777777778</v>
@@ -9997,10 +10531,10 @@
         <v>43830</v>
       </c>
       <c r="B502" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C502" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D502" s="5">
         <v>0.6597222222222222</v>
@@ -10011,10 +10545,10 @@
         <v>43830</v>
       </c>
       <c r="B503" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C503" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D503" s="5">
         <v>0.4097222222222222</v>
@@ -10025,10 +10559,10 @@
         <v>43830</v>
       </c>
       <c r="B504" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C504" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D504" s="5">
         <v>0.006944444444444444</v>
@@ -10039,10 +10573,10 @@
         <v>43830</v>
       </c>
       <c r="B505" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C505" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D505" s="5">
         <v>0.1875</v>
@@ -10053,10 +10587,10 @@
         <v>43830</v>
       </c>
       <c r="B506" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C506" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D506" s="5">
         <v>0.5347222222222222</v>
@@ -10067,10 +10601,10 @@
         <v>43830</v>
       </c>
       <c r="B507" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="C507" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D507" s="5">
         <v>0.03472222222222222</v>
@@ -10081,10 +10615,10 @@
         <v>43830</v>
       </c>
       <c r="B508" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C508" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D508" s="5">
         <v>0.5902777777777778</v>
@@ -10095,10 +10629,10 @@
         <v>43830</v>
       </c>
       <c r="B509" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="C509" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D509" s="5">
         <v>0.1458333333333333</v>
@@ -10109,10 +10643,10 @@
         <v>43830</v>
       </c>
       <c r="B510" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="C510" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D510" s="5">
         <v>0.7291666666666666</v>
@@ -10123,10 +10657,10 @@
         <v>43830</v>
       </c>
       <c r="B511" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="C511" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D511" s="5">
         <v>0.2013888888888889</v>
@@ -10137,10 +10671,10 @@
         <v>43830</v>
       </c>
       <c r="B512" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="C512" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D512" s="5">
         <v>0.7847222222222222</v>
@@ -10151,10 +10685,10 @@
         <v>43830</v>
       </c>
       <c r="B513" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="C513" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D513" s="5">
         <v>0.4236111111111111</v>
@@ -10165,10 +10699,10 @@
         <v>43830</v>
       </c>
       <c r="B514" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="C514" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D514" s="5">
         <v>0.9375</v>
@@ -10179,10 +10713,10 @@
         <v>43830</v>
       </c>
       <c r="B515" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
       <c r="C515" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D515" s="5">
         <v>0.04861111111111111</v>
@@ -10193,10 +10727,10 @@
         <v>43830</v>
       </c>
       <c r="B516" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="C516" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D516" s="5">
         <v>0.9236111111111112</v>
@@ -10207,10 +10741,10 @@
         <v>43830</v>
       </c>
       <c r="B517" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="C517" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D517" s="5">
         <v>0.7986111111111112</v>
@@ -10221,10 +10755,10 @@
         <v>43830</v>
       </c>
       <c r="B518" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="C518" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D518" s="5">
         <v>0.5486111111111112</v>
@@ -10235,10 +10769,10 @@
         <v>43830</v>
       </c>
       <c r="B519" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C519" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D519" s="5">
         <v>0.5208333333333334</v>
@@ -10249,10 +10783,10 @@
         <v>43830</v>
       </c>
       <c r="B520" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C520" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D520" s="5">
         <v>0.7013888888888888</v>
@@ -10263,10 +10797,10 @@
         <v>43830</v>
       </c>
       <c r="B521" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C521" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D521" s="5">
         <v>0.8819444444444444</v>
@@ -10277,10 +10811,10 @@
         <v>43830</v>
       </c>
       <c r="B522" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="C522" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D522" s="5">
         <v>0.8125</v>
@@ -10291,10 +10825,10 @@
         <v>43830</v>
       </c>
       <c r="B523" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C523" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D523" s="5">
         <v>0.2430555555555556</v>
@@ -10305,10 +10839,10 @@
         <v>43830</v>
       </c>
       <c r="B524" t="s">
-        <v>81</v>
+        <v>119</v>
       </c>
       <c r="C524" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D524" s="5">
         <v>0.3402777777777778</v>
@@ -10319,10 +10853,10 @@
         <v>43830</v>
       </c>
       <c r="B525" t="s">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="C525" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D525" s="5">
         <v>0.9652777777777778</v>
@@ -10333,10 +10867,10 @@
         <v>43830</v>
       </c>
       <c r="B526" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="C526" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D526" s="5">
         <v>0.3263888888888889</v>
@@ -10347,10 +10881,10 @@
         <v>43830</v>
       </c>
       <c r="B527" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C527" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D527" s="5">
         <v>0.8680555555555556</v>
@@ -10361,10 +10895,10 @@
         <v>43830</v>
       </c>
       <c r="B528" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="C528" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D528" s="5">
         <v>0.9791666666666666</v>
@@ -10375,10 +10909,10 @@
         <v>43830</v>
       </c>
       <c r="B529" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C529" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D529" s="5">
         <v>0.2708333333333333</v>
@@ -10389,10 +10923,10 @@
         <v>43830</v>
       </c>
       <c r="B530" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="C530" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D530" s="5">
         <v>0.7708333333333334</v>
@@ -10403,10 +10937,10 @@
         <v>43830</v>
       </c>
       <c r="B531" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="C531" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D531" s="5">
         <v>0.8541666666666666</v>
@@ -10417,10 +10951,10 @@
         <v>43830</v>
       </c>
       <c r="B532" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C532" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D532" s="5">
         <v>0.3680555555555556</v>
@@ -10431,10 +10965,10 @@
         <v>43830</v>
       </c>
       <c r="B533" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="C533" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D533" s="5">
         <v>0.6597222222222222</v>
@@ -10445,10 +10979,10 @@
         <v>43830</v>
       </c>
       <c r="B534" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="C534" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D534" s="5">
         <v>0.3819444444444444</v>
@@ -10459,10 +10993,10 @@
         <v>43830</v>
       </c>
       <c r="B535" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="C535" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D535" s="5">
         <v>0.1736111111111111</v>
@@ -10473,10 +11007,10 @@
         <v>43830</v>
       </c>
       <c r="B536" t="s">
-        <v>93</v>
+        <v>131</v>
       </c>
       <c r="C536" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D536" s="5">
         <v>0.1875</v>
@@ -10487,10 +11021,10 @@
         <v>43830</v>
       </c>
       <c r="B537" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="C537" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D537" s="5">
         <v>0.4791666666666667</v>
@@ -10501,10 +11035,10 @@
         <v>43830</v>
       </c>
       <c r="B538" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="C538" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D538" s="5">
         <v>0.6041666666666666</v>
@@ -10515,10 +11049,10 @@
         <v>43830</v>
       </c>
       <c r="B539" t="s">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c r="C539" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D539" s="5">
         <v>0.4930555555555556</v>
@@ -10529,10 +11063,10 @@
         <v>43830</v>
       </c>
       <c r="B540" t="s">
-        <v>97</v>
+        <v>135</v>
       </c>
       <c r="C540" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D540" s="5">
         <v>0.5763888888888888</v>
@@ -10543,10 +11077,10 @@
         <v>43830</v>
       </c>
       <c r="B541" t="s">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="C541" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D541" s="5">
         <v>0.5069444444444444</v>
@@ -10557,10 +11091,10 @@
         <v>43830</v>
       </c>
       <c r="B542" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="C542" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D542" s="5">
         <v>0.2569444444444444</v>
@@ -10571,10 +11105,10 @@
         <v>43830</v>
       </c>
       <c r="B543" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="C543" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D543" s="5">
         <v>0.2291666666666667</v>
@@ -10585,10 +11119,10 @@
         <v>43830</v>
       </c>
       <c r="B544" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="C544" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D544" s="5">
         <v>0.02083333333333333</v>
@@ -10599,10 +11133,10 @@
         <v>43830</v>
       </c>
       <c r="B545" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="C545" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D545" s="5">
         <v>0.6736111111111112</v>
@@ -10613,10 +11147,10 @@
         <v>43830</v>
       </c>
       <c r="B546" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C546" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D546" s="5">
         <v>0.9930555555555556</v>
@@ -10627,10 +11161,10 @@
         <v>43830</v>
       </c>
       <c r="B547" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C547" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D547" s="5">
         <v>0.2152777777777778</v>
@@ -10641,10 +11175,10 @@
         <v>43830</v>
       </c>
       <c r="B548" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C548" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D548" s="5">
         <v>0.3541666666666667</v>
@@ -10655,10 +11189,10 @@
         <v>43830</v>
       </c>
       <c r="B549" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="C549" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D549" s="5">
         <v>0.1319444444444444</v>
@@ -10669,10 +11203,10 @@
         <v>43830</v>
       </c>
       <c r="B550" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="C550" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D550" s="5">
         <v>0.8402777777777778</v>
@@ -10683,10 +11217,10 @@
         <v>43830</v>
       </c>
       <c r="B551" t="s">
-        <v>108</v>
+        <v>146</v>
       </c>
       <c r="C551" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D551" s="5">
         <v>0.1041666666666667</v>
@@ -10697,10 +11231,10 @@
         <v>43830</v>
       </c>
       <c r="B552" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="C552" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D552" s="5">
         <v>0.4652777777777778</v>
@@ -10711,10 +11245,10 @@
         <v>43830</v>
       </c>
       <c r="B553" t="s">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="C553" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D553" s="5">
         <v>0.6458333333333334</v>
@@ -10725,10 +11259,10 @@
         <v>43830</v>
       </c>
       <c r="B554" t="s">
-        <v>111</v>
+        <v>149</v>
       </c>
       <c r="C554" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D554" s="5">
         <v>0.6180555555555556</v>
@@ -10739,10 +11273,10 @@
         <v>43830</v>
       </c>
       <c r="B555" t="s">
-        <v>112</v>
+        <v>150</v>
       </c>
       <c r="C555" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D555" s="5">
         <v>0.4513888888888889</v>
@@ -10753,10 +11287,10 @@
         <v>43830</v>
       </c>
       <c r="B556" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="C556" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D556" s="5">
         <v>0.6875</v>
@@ -10767,10 +11301,10 @@
         <v>43830</v>
       </c>
       <c r="B557" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C557" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D557" s="5">
         <v>0.7569444444444444</v>
@@ -10781,10 +11315,10 @@
         <v>43830</v>
       </c>
       <c r="B558" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="C558" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D558" s="5">
         <v>0.4097222222222222</v>
@@ -10795,10 +11329,10 @@
         <v>43830</v>
       </c>
       <c r="B559" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="C559" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D559" s="5">
         <v>0.5625</v>
@@ -10809,10 +11343,10 @@
         <v>43830</v>
       </c>
       <c r="B560" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="C560" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D560" s="5">
         <v>0.0763888888888889</v>
@@ -10823,10 +11357,10 @@
         <v>43830</v>
       </c>
       <c r="B561" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="C561" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D561" s="5">
         <v>0.7152777777777778</v>
@@ -10837,10 +11371,10 @@
         <v>43830</v>
       </c>
       <c r="B562" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C562" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D562" s="5">
         <v>0.8958333333333334</v>
@@ -10851,10 +11385,10 @@
         <v>43830</v>
       </c>
       <c r="B563" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="C563" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D563" s="5">
         <v>0.3958333333333333</v>
@@ -10865,10 +11399,10 @@
         <v>43830</v>
       </c>
       <c r="B564" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C564" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D564" s="5">
         <v>0.2847222222222222</v>
@@ -10879,10 +11413,10 @@
         <v>43830</v>
       </c>
       <c r="B565" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="C565" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D565" s="5">
         <v>0.6319444444444444</v>
@@ -10893,10 +11427,10 @@
         <v>43830</v>
       </c>
       <c r="B566" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="C566" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D566" s="5">
         <v>0.2986111111111111</v>
@@ -10907,10 +11441,10 @@
         <v>43830</v>
       </c>
       <c r="B567" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="C567" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D567" s="5">
         <v>0.09027777777777778</v>
@@ -10921,10 +11455,10 @@
         <v>43830</v>
       </c>
       <c r="B568" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="C568" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D568" s="5">
         <v>0.9513888888888888</v>
@@ -10935,10 +11469,10 @@
         <v>43830</v>
       </c>
       <c r="B569" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C569" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D569" s="5">
         <v>0.1597222222222222</v>
@@ -10949,10 +11483,10 @@
         <v>43830</v>
       </c>
       <c r="B570" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="C570" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D570" s="5">
         <v>0.0625</v>
@@ -10963,10 +11497,10 @@
         <v>43830</v>
       </c>
       <c r="B571" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="C571" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D571" s="5">
         <v>0.7430555555555556</v>
@@ -10977,10 +11511,10 @@
         <v>43830</v>
       </c>
       <c r="B572" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="C572" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D572" s="5">
         <v>0.006944444444444444</v>
@@ -10991,10 +11525,10 @@
         <v>43830</v>
       </c>
       <c r="B573" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C573" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D573" s="5">
         <v>0.9097222222222222</v>
@@ -11005,10 +11539,10 @@
         <v>43830</v>
       </c>
       <c r="B574" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="C574" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D574" s="5">
         <v>0.8263888888888888</v>
@@ -11019,10 +11553,10 @@
         <v>43830</v>
       </c>
       <c r="B575" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="C575" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D575" s="5">
         <v>0.4375</v>
@@ -11033,10 +11567,10 @@
         <v>43830</v>
       </c>
       <c r="B576" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C576" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D576" s="5">
         <v>0.1180555555555556</v>
@@ -11047,10 +11581,10 @@
         <v>43830</v>
       </c>
       <c r="B577" t="s">
-        <v>134</v>
+        <v>172</v>
       </c>
       <c r="C577" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D577" s="5">
         <v>0.3125</v>
@@ -11073,15 +11607,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="2" customFormat="1" ht="24" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>141</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="B2" s="8" t="b">
         <v>1</v>
@@ -11089,15 +11623,15 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>11</v>
@@ -11105,15 +11639,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>184</v>
       </c>
       <c r="B6" s="8">
         <v>500000</v>
@@ -11121,7 +11655,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="B7" s="8" t="b">
         <v>1</v>
@@ -11129,7 +11663,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>186</v>
       </c>
       <c r="B8" s="8" t="b">
         <v>1</v>
@@ -11137,7 +11671,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="B9" s="8" t="b">
         <v>1</v>
@@ -11145,7 +11679,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="B10" s="8" t="b">
         <v>1</v>
@@ -11153,7 +11687,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>189</v>
       </c>
       <c r="B11" s="8" t="b">
         <v>1</v>
@@ -11161,7 +11695,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="B12" s="8" t="b">
         <v>1</v>
@@ -11169,7 +11703,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>191</v>
       </c>
       <c r="B13" s="8" t="b">
         <v>1</v>
@@ -11177,7 +11711,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="B14" s="8" t="b">
         <v>1</v>
@@ -11185,7 +11719,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="B15" s="8" t="b">
         <v>1</v>
@@ -11193,7 +11727,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="B16" s="8" t="b">
         <v>1</v>
@@ -11201,7 +11735,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="B17" s="8" t="b">
         <v>1</v>
@@ -11209,7 +11743,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="B18" s="8" t="b">
         <v>1</v>
